--- a/www/flightdata/xlsx/eoss-361.xlsx
+++ b/www/flightdata/xlsx/eoss-361.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3109" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="1088">
   <si>
     <t>flight</t>
   </si>
@@ -147,7 +147,7 @@
     <t>415</t>
   </si>
   <si>
-    <t>1hrs 35mins 30secs</t>
+    <t>1hrs 34mins 53secs</t>
   </si>
   <si>
     <t>flightid</t>
@@ -2673,9 +2673,6 @@
     <t>/155838h3849.13N/10357.97WO117/000/A=005610 359T8337P EOSS BALLOON</t>
   </si>
   <si>
-    <t>/155915h3849.12N/10357.97WO083/000/A=005621 180T8368P EOSS Balloon</t>
-  </si>
-  <si>
     <t>KC0D-2&gt;APZEOS,EOSS,WIDE2-1,qAO,AE0SS-9:/151745h3859.85N/10357.92WO262/041/A=095968 133T136P EOSS Balloon</t>
   </si>
   <si>
@@ -3280,9 +3277,6 @@
   </si>
   <si>
     <t>AE0SS-2&gt;APZEOS,EOSS*,WIDE2-1,qAO,W9CN-9:/155838h3849.13N/10357.97WO117/000/A=005610 359T8337P EOSS BALLOON</t>
-  </si>
-  <si>
-    <t>KC0D-2&gt;APZEOS,EOSS*,WIDE2-1,qAO,W9CN-9:/155915h3849.12N/10357.97WO083/000/A=005621 180T8368P EOSS Balloon</t>
   </si>
   <si>
     <t>n/a</t>
@@ -3789,19 +3783,19 @@
         <v>30216.65</v>
       </c>
       <c r="I2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
       </c>
       <c r="K2">
-        <v>5730</v>
+        <v>5693</v>
       </c>
       <c r="L2">
-        <v>27.05</v>
+        <v>27.04</v>
       </c>
       <c r="M2">
-        <v>43.53</v>
+        <v>43.51</v>
       </c>
       <c r="N2">
         <v>12.29</v>
@@ -3858,22 +3852,22 @@
         <v>8707.219999999999</v>
       </c>
       <c r="AF2">
-        <v>38.8186666667</v>
+        <v>38.8188333333</v>
       </c>
       <c r="AG2">
         <v>-103.9661666667</v>
       </c>
       <c r="AH2">
-        <v>27.05</v>
+        <v>27.04</v>
       </c>
       <c r="AI2">
-        <v>43.53</v>
+        <v>43.51</v>
       </c>
       <c r="AJ2">
-        <v>5621</v>
+        <v>5610</v>
       </c>
       <c r="AK2">
-        <v>1713.28</v>
+        <v>1709.93</v>
       </c>
     </row>
   </sheetData>
@@ -44871,7 +44865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU204"/>
+  <dimension ref="A1:AU203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:47">
@@ -45049,7 +45043,7 @@
         <v>683</v>
       </c>
       <c r="K2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="L2">
         <v>262</v>
@@ -45106,19 +45100,19 @@
         <v>-32.18666667</v>
       </c>
       <c r="AD2" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AF2">
         <v>-105.6</v>
       </c>
       <c r="AL2">
-        <v>-105.385293</v>
+        <v>-105.379219</v>
       </c>
       <c r="AN2">
         <v>-32.186667</v>
       </c>
       <c r="AT2">
-        <v>-32.121225</v>
+        <v>-32.119373</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -45153,7 +45147,7 @@
         <v>684</v>
       </c>
       <c r="K3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="L3">
         <v>286</v>
@@ -45210,7 +45204,7 @@
         <v>-21.22175</v>
       </c>
       <c r="AD3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE3">
         <v>0.299792</v>
@@ -45228,7 +45222,7 @@
         <v>0.707107</v>
       </c>
       <c r="AL3">
-        <v>-82.57304600000001</v>
+        <v>-82.776143</v>
       </c>
       <c r="AM3">
         <v>0.091374</v>
@@ -45246,7 +45240,7 @@
         <v>0.707107</v>
       </c>
       <c r="AT3">
-        <v>-25.168368</v>
+        <v>-25.230273</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -45281,7 +45275,7 @@
         <v>685</v>
       </c>
       <c r="K4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="L4">
         <v>236</v>
@@ -45338,7 +45332,7 @@
         <v>-33.57544444</v>
       </c>
       <c r="AD4" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE4">
         <v>-0.45034</v>
@@ -45362,7 +45356,7 @@
         <v>-0.707107</v>
       </c>
       <c r="AL4">
-        <v>-102.623032</v>
+        <v>-102.558702</v>
       </c>
       <c r="AM4">
         <v>-0.137263</v>
@@ -45386,7 +45380,7 @@
         <v>-0.707109</v>
       </c>
       <c r="AT4">
-        <v>-31.27951</v>
+        <v>-31.259902</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -45421,7 +45415,7 @@
         <v>686</v>
       </c>
       <c r="K5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L5">
         <v>267</v>
@@ -45478,7 +45472,7 @@
         <v>-39.177</v>
       </c>
       <c r="AD5" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE5">
         <v>-0.306296</v>
@@ -45502,7 +45496,7 @@
         <v>-0.386898</v>
       </c>
       <c r="AL5">
-        <v>-115.133313</v>
+        <v>-114.938043</v>
       </c>
       <c r="AM5">
         <v>-0.093359</v>
@@ -45526,7 +45520,7 @@
         <v>-0.386897</v>
       </c>
       <c r="AT5">
-        <v>-35.092622</v>
+        <v>-35.033102</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -45561,7 +45555,7 @@
         <v>687</v>
       </c>
       <c r="K6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L6">
         <v>276</v>
@@ -45618,7 +45612,7 @@
         <v>-35.22466667</v>
       </c>
       <c r="AD6" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE6">
         <v>0.432222</v>
@@ -45642,7 +45636,7 @@
         <v>1.002928</v>
       </c>
       <c r="AL6">
-        <v>-126.788813</v>
+        <v>-126.696823</v>
       </c>
       <c r="AM6">
         <v>0.131744</v>
@@ -45666,7 +45660,7 @@
         <v>1.00295</v>
       </c>
       <c r="AT6">
-        <v>-38.645261</v>
+        <v>-38.617221</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -45701,7 +45695,7 @@
         <v>688</v>
       </c>
       <c r="K7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="L7">
         <v>281</v>
@@ -45758,7 +45752,7 @@
         <v>-34.3815</v>
       </c>
       <c r="AD7" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE7">
         <v>0.046111</v>
@@ -45782,7 +45776,7 @@
         <v>0.110249</v>
       </c>
       <c r="AL7">
-        <v>-112.849498</v>
+        <v>-112.948985</v>
       </c>
       <c r="AM7">
         <v>0.014053</v>
@@ -45806,7 +45800,7 @@
         <v>0.110235</v>
       </c>
       <c r="AT7">
-        <v>-34.396536</v>
+        <v>-34.42686</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -45841,7 +45835,7 @@
         <v>689</v>
       </c>
       <c r="K8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="L8">
         <v>273</v>
@@ -45898,7 +45892,7 @@
         <v>-32.502</v>
       </c>
       <c r="AD8" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE8">
         <v>0.205556</v>
@@ -45922,7 +45916,7 @@
         <v>0.48052</v>
       </c>
       <c r="AL8">
-        <v>-109.17744</v>
+        <v>-109.296088</v>
       </c>
       <c r="AM8">
         <v>0.06265</v>
@@ -45946,7 +45940,7 @@
         <v>0.4805</v>
       </c>
       <c r="AT8">
-        <v>-33.277307</v>
+        <v>-33.313472</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -45981,7 +45975,7 @@
         <v>690</v>
       </c>
       <c r="K9" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="L9">
         <v>217</v>
@@ -46038,7 +46032,7 @@
         <v>-30.52066667</v>
       </c>
       <c r="AD9" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE9">
         <v>0.216667</v>
@@ -46062,7 +46056,7 @@
         <v>0.470606</v>
       </c>
       <c r="AL9">
-        <v>-98.501131</v>
+        <v>-98.59156</v>
       </c>
       <c r="AM9">
         <v>0.06604400000000001</v>
@@ -46086,7 +46080,7 @@
         <v>0.470647</v>
       </c>
       <c r="AT9">
-        <v>-30.023164</v>
+        <v>-30.050728</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -46121,7 +46115,7 @@
         <v>691</v>
       </c>
       <c r="K10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="L10">
         <v>280</v>
@@ -46178,7 +46172,7 @@
         <v>-30.175</v>
       </c>
       <c r="AD10" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE10">
         <v>0.037778</v>
@@ -46202,7 +46196,7 @@
         <v>-0.074277</v>
       </c>
       <c r="AL10">
-        <v>-96.63814000000001</v>
+        <v>-96.70412</v>
       </c>
       <c r="AM10">
         <v>0.011522</v>
@@ -46226,7 +46220,7 @@
         <v>-0.074212</v>
       </c>
       <c r="AT10">
-        <v>-29.45535</v>
+        <v>-29.475462</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -46261,7 +46255,7 @@
         <v>692</v>
       </c>
       <c r="K11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="L11">
         <v>250</v>
@@ -46318,7 +46312,7 @@
         <v>-27.95033333</v>
       </c>
       <c r="AD11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE11">
         <v>0.243333</v>
@@ -46342,7 +46336,7 @@
         <v>0.563846</v>
       </c>
       <c r="AL11">
-        <v>-91.67032500000001</v>
+        <v>-91.614617</v>
       </c>
       <c r="AM11">
         <v>0.074156</v>
@@ -46366,7 +46360,7 @@
         <v>0.563719</v>
       </c>
       <c r="AT11">
-        <v>-27.941134</v>
+        <v>-27.924154</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -46401,7 +46395,7 @@
         <v>693</v>
       </c>
       <c r="K12" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L12">
         <v>284</v>
@@ -46458,7 +46452,7 @@
         <v>-31.31713333</v>
       </c>
       <c r="AD12" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE12">
         <v>-0.073644</v>
@@ -46482,7 +46476,7 @@
         <v>-0.50177</v>
       </c>
       <c r="AL12">
-        <v>-90.254644</v>
+        <v>-90.16124499999999</v>
       </c>
       <c r="AM12">
         <v>-0.022445</v>
@@ -46506,7 +46500,7 @@
         <v>-0.501756</v>
       </c>
       <c r="AT12">
-        <v>-27.50963</v>
+        <v>-27.481161</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -46541,7 +46535,7 @@
         <v>694</v>
       </c>
       <c r="K13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L13">
         <v>237</v>
@@ -46598,7 +46592,7 @@
         <v>-27.498</v>
       </c>
       <c r="AD13" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE13">
         <v>0.208833</v>
@@ -46622,7 +46616,7 @@
         <v>0.491335</v>
       </c>
       <c r="AL13">
-        <v>-89.64521499999999</v>
+        <v>-89.544639</v>
       </c>
       <c r="AM13">
         <v>0.063652</v>
@@ -46646,7 +46640,7 @@
         <v>0.491338</v>
       </c>
       <c r="AT13">
-        <v>-27.323866</v>
+        <v>-27.293209</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -46681,7 +46675,7 @@
         <v>695</v>
       </c>
       <c r="K14" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="L14">
         <v>260</v>
@@ -46738,7 +46732,7 @@
         <v>-26.284</v>
       </c>
       <c r="AD14" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE14">
         <v>0.132778</v>
@@ -46762,7 +46756,7 @@
         <v>0.197014</v>
       </c>
       <c r="AL14">
-        <v>-89.09093799999999</v>
+        <v>-88.98899299999999</v>
       </c>
       <c r="AM14">
         <v>0.040467</v>
@@ -46786,7 +46780,7 @@
         <v>0.196978</v>
       </c>
       <c r="AT14">
-        <v>-27.154917</v>
+        <v>-27.123843</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -46821,7 +46815,7 @@
         <v>696</v>
       </c>
       <c r="K15" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="L15">
         <v>303</v>
@@ -46878,7 +46872,7 @@
         <v>-25.776</v>
       </c>
       <c r="AD15" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE15">
         <v>0.055556</v>
@@ -46902,7 +46896,7 @@
         <v>-0.103097</v>
       </c>
       <c r="AL15">
-        <v>-86.342551</v>
+        <v>-86.26967</v>
       </c>
       <c r="AM15">
         <v>0.016933</v>
@@ -46926,7 +46920,7 @@
         <v>-0.103094</v>
       </c>
       <c r="AT15">
-        <v>-26.317193</v>
+        <v>-26.294978</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -46961,7 +46955,7 @@
         <v>697</v>
       </c>
       <c r="K16" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="L16">
         <v>252</v>
@@ -47018,7 +47012,7 @@
         <v>-25.26766667</v>
       </c>
       <c r="AD16" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE16">
         <v>0.055556</v>
@@ -47042,7 +47036,7 @@
         <v>-0.09959999999999999</v>
       </c>
       <c r="AL16">
-        <v>-85.48940399999999</v>
+        <v>-85.429732</v>
       </c>
       <c r="AM16">
         <v>0.016944</v>
@@ -47066,7 +47060,7 @@
         <v>-0.09946099999999999</v>
       </c>
       <c r="AT16">
-        <v>-26.057167</v>
+        <v>-26.038979</v>
       </c>
     </row>
     <row r="17" spans="1:46">
@@ -47101,7 +47095,7 @@
         <v>698</v>
       </c>
       <c r="K17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="L17">
         <v>273</v>
@@ -47158,7 +47152,7 @@
         <v>-25.09533333</v>
       </c>
       <c r="AD17" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE17">
         <v>0.009443999999999999</v>
@@ -47182,7 +47176,7 @@
         <v>-0.286531</v>
       </c>
       <c r="AL17">
-        <v>-82.810821</v>
+        <v>-82.792812</v>
       </c>
       <c r="AM17">
         <v>0.002872</v>
@@ -47206,7 +47200,7 @@
         <v>-0.286629</v>
       </c>
       <c r="AT17">
-        <v>-25.240714</v>
+        <v>-25.235225</v>
       </c>
     </row>
     <row r="18" spans="1:46">
@@ -47241,7 +47235,7 @@
         <v>699</v>
       </c>
       <c r="K18" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="L18">
         <v>226</v>
@@ -47298,7 +47292,7 @@
         <v>-22.49433333</v>
       </c>
       <c r="AD18" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE18">
         <v>0.284444</v>
@@ -47322,7 +47316,7 @@
         <v>0.877292</v>
       </c>
       <c r="AL18">
-        <v>-80.591413</v>
+        <v>-80.60463300000001</v>
       </c>
       <c r="AM18">
         <v>0.0867</v>
@@ -47346,7 +47340,7 @@
         <v>0.877322</v>
       </c>
       <c r="AT18">
-        <v>-24.56425</v>
+        <v>-24.568279</v>
       </c>
     </row>
     <row r="19" spans="1:46">
@@ -47381,7 +47375,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="L19">
         <v>80</v>
@@ -47438,7 +47432,7 @@
         <v>-22.047</v>
       </c>
       <c r="AD19" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE19">
         <v>0.048889</v>
@@ -47462,7 +47456,7 @@
         <v>-0.166319</v>
       </c>
       <c r="AL19">
-        <v>-77.28737</v>
+        <v>-77.338466</v>
       </c>
       <c r="AM19">
         <v>0.014911</v>
@@ -47486,7 +47480,7 @@
         <v>-0.166187</v>
       </c>
       <c r="AT19">
-        <v>-23.557179</v>
+        <v>-23.572753</v>
       </c>
     </row>
     <row r="20" spans="1:46">
@@ -47521,7 +47515,7 @@
         <v>701</v>
       </c>
       <c r="K20" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L20">
         <v>263</v>
@@ -47578,7 +47572,7 @@
         <v>-22.088</v>
       </c>
       <c r="AD20" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE20">
         <v>-0.004444</v>
@@ -47602,7 +47596,7 @@
         <v>-0.398406</v>
       </c>
       <c r="AL20">
-        <v>-74.705129</v>
+        <v>-74.777603</v>
       </c>
       <c r="AM20">
         <v>-0.001367</v>
@@ -47626,7 +47620,7 @@
         <v>-0.398606</v>
       </c>
       <c r="AT20">
-        <v>-22.770099</v>
+        <v>-22.792189</v>
       </c>
     </row>
     <row r="21" spans="1:46">
@@ -47661,7 +47655,7 @@
         <v>702</v>
       </c>
       <c r="K21" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L21">
         <v>156</v>
@@ -47718,7 +47712,7 @@
         <v>-21.99633333</v>
       </c>
       <c r="AD21" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE21">
         <v>0.01</v>
@@ -47742,7 +47736,7 @@
         <v>-0.32107</v>
       </c>
       <c r="AL21">
-        <v>-71.218693</v>
+        <v>-71.30739199999999</v>
       </c>
       <c r="AM21">
         <v>0.003056</v>
@@ -47766,7 +47760,7 @@
         <v>-0.320949</v>
       </c>
       <c r="AT21">
-        <v>-21.707456</v>
+        <v>-21.734493</v>
       </c>
     </row>
     <row r="22" spans="1:46">
@@ -47801,7 +47795,7 @@
         <v>703</v>
       </c>
       <c r="K22" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="L22">
         <v>209</v>
@@ -47858,7 +47852,7 @@
         <v>-22.00311111</v>
       </c>
       <c r="AD22" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE22">
         <v>-0.000247</v>
@@ -47882,7 +47876,7 @@
         <v>-0.360408</v>
       </c>
       <c r="AL22">
-        <v>-70.14055</v>
+        <v>-70.231111</v>
       </c>
       <c r="AM22">
         <v>-7.499999999999999E-05</v>
@@ -47906,7 +47900,7 @@
         <v>-0.360403</v>
       </c>
       <c r="AT22">
-        <v>-21.378832</v>
+        <v>-21.406436</v>
       </c>
     </row>
     <row r="23" spans="1:46">
@@ -47941,7 +47935,7 @@
         <v>704</v>
       </c>
       <c r="K23" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L23">
         <v>219</v>
@@ -47998,7 +47992,7 @@
         <v>-21.30533333</v>
       </c>
       <c r="AD23" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE23">
         <v>0.076296</v>
@@ -48022,7 +48016,7 @@
         <v>0.017873</v>
       </c>
       <c r="AL23">
-        <v>-68.86228</v>
+        <v>-68.952996</v>
       </c>
       <c r="AM23">
         <v>0.023259</v>
@@ -48046,7 +48040,7 @@
         <v>0.017936</v>
       </c>
       <c r="AT23">
-        <v>-20.98922</v>
+        <v>-21.016871</v>
       </c>
     </row>
     <row r="24" spans="1:46">
@@ -48081,7 +48075,7 @@
         <v>705</v>
       </c>
       <c r="K24" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L24">
         <v>336</v>
@@ -48138,7 +48132,7 @@
         <v>-20.58433333</v>
       </c>
       <c r="AD24" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE24">
         <v>0.078889</v>
@@ -48162,7 +48156,7 @@
         <v>0.030354</v>
       </c>
       <c r="AL24">
-        <v>-65.82334299999999</v>
+        <v>-65.904932</v>
       </c>
       <c r="AM24">
         <v>0.024033</v>
@@ -48186,7 +48180,7 @@
         <v>0.030153</v>
       </c>
       <c r="AT24">
-        <v>-20.062948</v>
+        <v>-20.087816</v>
       </c>
     </row>
     <row r="25" spans="1:46">
@@ -48221,7 +48215,7 @@
         <v>706</v>
       </c>
       <c r="K25" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="L25">
         <v>316</v>
@@ -48278,7 +48272,7 @@
         <v>-20.056</v>
       </c>
       <c r="AD25" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE25">
         <v>0.057778</v>
@@ -48302,7 +48296,7 @@
         <v>-0.07777299999999999</v>
       </c>
       <c r="AL25">
-        <v>-63.878927</v>
+        <v>-63.947179</v>
       </c>
       <c r="AM25">
         <v>0.017611</v>
@@ -48326,7 +48320,7 @@
         <v>-0.077765</v>
       </c>
       <c r="AT25">
-        <v>-19.47029</v>
+        <v>-19.491094</v>
       </c>
     </row>
     <row r="26" spans="1:46">
@@ -48361,7 +48355,7 @@
         <v>707</v>
       </c>
       <c r="K26" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L26">
         <v>268</v>
@@ -48418,7 +48412,7 @@
         <v>-18.43033333</v>
       </c>
       <c r="AD26" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE26">
         <v>0.177778</v>
@@ -48442,7 +48436,7 @@
         <v>0.545953</v>
       </c>
       <c r="AL26">
-        <v>-61.650712</v>
+        <v>-61.696076</v>
       </c>
       <c r="AM26">
         <v>0.054189</v>
@@ -48466,7 +48460,7 @@
         <v>0.545987</v>
       </c>
       <c r="AT26">
-        <v>-18.791132</v>
+        <v>-18.804959</v>
       </c>
     </row>
     <row r="27" spans="1:46">
@@ -48501,7 +48495,7 @@
         <v>708</v>
       </c>
       <c r="K27" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L27">
         <v>119</v>
@@ -48558,7 +48552,7 @@
         <v>-19.73583333</v>
       </c>
       <c r="AD27" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE27">
         <v>-0.07138899999999999</v>
@@ -48582,7 +48576,7 @@
         <v>-0.775132</v>
       </c>
       <c r="AL27">
-        <v>-60.763764</v>
+        <v>-60.797757</v>
       </c>
       <c r="AM27">
         <v>-0.021758</v>
@@ -48606,7 +48600,7 @@
         <v>-0.775106</v>
       </c>
       <c r="AT27">
-        <v>-18.520799</v>
+        <v>-18.53116</v>
       </c>
     </row>
     <row r="28" spans="1:46">
@@ -48641,7 +48635,7 @@
         <v>709</v>
       </c>
       <c r="K28" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="L28">
         <v>300</v>
@@ -48698,7 +48692,7 @@
         <v>-18.15566667</v>
       </c>
       <c r="AD28" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE28">
         <v>0.172778</v>
@@ -48722,7 +48716,7 @@
         <v>0.541734</v>
       </c>
       <c r="AL28">
-        <v>-60.089642</v>
+        <v>-60.114173</v>
       </c>
       <c r="AM28">
         <v>0.052672</v>
@@ -48746,7 +48740,7 @@
         <v>0.541911</v>
       </c>
       <c r="AT28">
-        <v>-18.31534</v>
+        <v>-18.322817</v>
       </c>
     </row>
     <row r="29" spans="1:46">
@@ -48781,7 +48775,7 @@
         <v>710</v>
       </c>
       <c r="K29" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="L29">
         <v>202</v>
@@ -48838,7 +48832,7 @@
         <v>-18.298</v>
       </c>
       <c r="AD29" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE29">
         <v>-0.015556</v>
@@ -48862,7 +48856,7 @@
         <v>-0.488005</v>
       </c>
       <c r="AL29">
-        <v>-58.247003</v>
+        <v>-58.24256</v>
       </c>
       <c r="AM29">
         <v>-0.004744</v>
@@ -48886,7 +48880,7 @@
         <v>-0.488063</v>
       </c>
       <c r="AT29">
-        <v>-17.753698</v>
+        <v>-17.752344</v>
       </c>
     </row>
     <row r="30" spans="1:46">
@@ -48921,7 +48915,7 @@
         <v>711</v>
       </c>
       <c r="K30" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="L30">
         <v>215</v>
@@ -48978,7 +48972,7 @@
         <v>-17.80033333</v>
       </c>
       <c r="AD30" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE30">
         <v>0.054444</v>
@@ -49002,7 +48996,7 @@
         <v>-0.09361999999999999</v>
       </c>
       <c r="AL30">
-        <v>-57.060501</v>
+        <v>-57.035824</v>
       </c>
       <c r="AM30">
         <v>0.016589</v>
@@ -49026,7 +49020,7 @@
         <v>-0.09371400000000001</v>
       </c>
       <c r="AT30">
-        <v>-17.392061</v>
+        <v>-17.384539</v>
       </c>
     </row>
     <row r="31" spans="1:46">
@@ -49061,7 +49055,7 @@
         <v>712</v>
       </c>
       <c r="K31" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L31">
         <v>246</v>
@@ -49118,7 +49112,7 @@
         <v>-17.333</v>
       </c>
       <c r="AD31" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE31">
         <v>0.051111</v>
@@ -49142,7 +49136,7 @@
         <v>-0.110756</v>
       </c>
       <c r="AL31">
-        <v>-55.61564</v>
+        <v>-55.566627</v>
       </c>
       <c r="AM31">
         <v>0.015578</v>
@@ -49166,7 +49160,7 @@
         <v>-0.110763</v>
       </c>
       <c r="AT31">
-        <v>-16.951661</v>
+        <v>-16.936722</v>
       </c>
     </row>
     <row r="32" spans="1:46">
@@ -49201,7 +49195,7 @@
         <v>713</v>
       </c>
       <c r="K32" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="L32">
         <v>198</v>
@@ -49258,7 +49252,7 @@
         <v>-17.77483333</v>
       </c>
       <c r="AD32" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE32">
         <v>-0.024167</v>
@@ -49282,7 +49276,7 @@
         <v>-0.537162</v>
       </c>
       <c r="AL32">
-        <v>-55.026472</v>
+        <v>-54.968335</v>
       </c>
       <c r="AM32">
         <v>-0.007364</v>
@@ -49306,7 +49300,7 @@
         <v>-0.537126</v>
       </c>
       <c r="AT32">
-        <v>-16.77209</v>
+        <v>-16.75437</v>
       </c>
     </row>
     <row r="33" spans="1:46">
@@ -49341,7 +49335,7 @@
         <v>714</v>
       </c>
       <c r="K33" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="L33">
         <v>218</v>
@@ -49398,7 +49392,7 @@
         <v>-16.947</v>
       </c>
       <c r="AD33" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE33">
         <v>0.090556</v>
@@ -49422,7 +49416,7 @@
         <v>0.136583</v>
       </c>
       <c r="AL33">
-        <v>-54.668955</v>
+        <v>-54.605692</v>
       </c>
       <c r="AM33">
         <v>0.027594</v>
@@ -49446,7 +49440,7 @@
         <v>0.13643</v>
       </c>
       <c r="AT33">
-        <v>-16.663115</v>
+        <v>-16.643832</v>
       </c>
     </row>
     <row r="34" spans="1:46">
@@ -49481,7 +49475,7 @@
         <v>715</v>
       </c>
       <c r="K34" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L34">
         <v>63</v>
@@ -49538,7 +49532,7 @@
         <v>-15.606</v>
       </c>
       <c r="AD34" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE34">
         <v>0.146667</v>
@@ -49562,7 +49556,7 @@
         <v>0.46387</v>
       </c>
       <c r="AL34">
-        <v>-53.040837</v>
+        <v>-52.960192</v>
       </c>
       <c r="AM34">
         <v>0.0447</v>
@@ -49586,7 +49580,7 @@
         <v>0.463796</v>
       </c>
       <c r="AT34">
-        <v>-16.16686</v>
+        <v>-16.142279</v>
       </c>
     </row>
     <row r="35" spans="1:46">
@@ -49621,7 +49615,7 @@
         <v>716</v>
       </c>
       <c r="K35" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L35">
         <v>132</v>
@@ -49678,7 +49672,7 @@
         <v>-15.687</v>
       </c>
       <c r="AD35" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE35">
         <v>-0.008888999999999999</v>
@@ -49702,7 +49696,7 @@
         <v>-0.471281</v>
       </c>
       <c r="AL35">
-        <v>-52.700556</v>
+        <v>-52.617851</v>
       </c>
       <c r="AM35">
         <v>-0.0027</v>
@@ -49726,7 +49720,7 @@
         <v>-0.471098</v>
       </c>
       <c r="AT35">
-        <v>-16.063149</v>
+        <v>-16.03794</v>
       </c>
     </row>
     <row r="36" spans="1:46">
@@ -49761,7 +49755,7 @@
         <v>717</v>
       </c>
       <c r="K36" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -49818,7 +49812,7 @@
         <v>-15.91566667</v>
       </c>
       <c r="AD36" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE36">
         <v>-0.0125</v>
@@ -49842,7 +49836,7 @@
         <v>-0.484586</v>
       </c>
       <c r="AL36">
-        <v>-51.594631</v>
+        <v>-51.50965</v>
       </c>
       <c r="AM36">
         <v>-0.003811</v>
@@ -49866,7 +49860,7 @@
         <v>-0.484604</v>
       </c>
       <c r="AT36">
-        <v>-15.726057</v>
+        <v>-15.700154</v>
       </c>
     </row>
     <row r="37" spans="1:46">
@@ -49901,7 +49895,7 @@
         <v>718</v>
       </c>
       <c r="K37" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="L37">
         <v>3</v>
@@ -49958,7 +49952,7 @@
         <v>-15.60566667</v>
       </c>
       <c r="AD37" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE37">
         <v>0.033889</v>
@@ -49982,7 +49976,7 @@
         <v>-0.193406</v>
       </c>
       <c r="AL37">
-        <v>-50.802659</v>
+        <v>-50.720228</v>
       </c>
       <c r="AM37">
         <v>0.010333</v>
@@ -50006,7 +50000,7 @@
         <v>-0.193343</v>
       </c>
       <c r="AT37">
-        <v>-15.484672</v>
+        <v>-15.459546</v>
       </c>
     </row>
     <row r="38" spans="1:46">
@@ -50041,7 +50035,7 @@
         <v>719</v>
       </c>
       <c r="K38" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L38">
         <v>2</v>
@@ -50098,7 +50092,7 @@
         <v>-14.83366667</v>
       </c>
       <c r="AD38" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE38">
         <v>0.08444400000000001</v>
@@ -50122,7 +50116,7 @@
         <v>0.123635</v>
       </c>
       <c r="AL38">
-        <v>-49.764576</v>
+        <v>-49.690251</v>
       </c>
       <c r="AM38">
         <v>0.025733</v>
@@ -50146,7 +50140,7 @@
         <v>0.123515</v>
       </c>
       <c r="AT38">
-        <v>-15.168251</v>
+        <v>-15.145596</v>
       </c>
     </row>
     <row r="39" spans="1:46">
@@ -50181,7 +50175,7 @@
         <v>720</v>
       </c>
       <c r="K39" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L39">
         <v>190</v>
@@ -50238,7 +50232,7 @@
         <v>-15.12316667</v>
       </c>
       <c r="AD39" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE39">
         <v>-0.015833</v>
@@ -50262,7 +50256,7 @@
         <v>-0.509006</v>
       </c>
       <c r="AL39">
-        <v>-49.317119</v>
+        <v>-49.247706</v>
       </c>
       <c r="AM39">
         <v>-0.004825</v>
@@ -50286,7 +50280,7 @@
         <v>-0.5089900000000001</v>
       </c>
       <c r="AT39">
-        <v>-15.031866</v>
+        <v>-15.010709</v>
       </c>
     </row>
     <row r="40" spans="1:46">
@@ -50321,7 +50315,7 @@
         <v>721</v>
       </c>
       <c r="K40" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L40">
         <v>309</v>
@@ -50378,7 +50372,7 @@
         <v>-14.16333333</v>
       </c>
       <c r="AD40" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE40">
         <v>0.105</v>
@@ -50402,7 +50396,7 @@
         <v>0.268135</v>
       </c>
       <c r="AL40">
-        <v>-49.019781</v>
+        <v>-48.954027</v>
       </c>
       <c r="AM40">
         <v>0.031994</v>
@@ -50426,7 +50420,7 @@
         <v>0.267937</v>
       </c>
       <c r="AT40">
-        <v>-14.941236</v>
+        <v>-14.921194</v>
       </c>
     </row>
     <row r="41" spans="1:46">
@@ -50461,7 +50455,7 @@
         <v>722</v>
       </c>
       <c r="K41" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="L41">
         <v>52</v>
@@ -50518,7 +50512,7 @@
         <v>-14.14266667</v>
       </c>
       <c r="AD41" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE41">
         <v>0.002222</v>
@@ -50542,7 +50536,7 @@
         <v>-0.39864</v>
       </c>
       <c r="AL41">
-        <v>-47.919901</v>
+        <v>-47.869875</v>
       </c>
       <c r="AM41">
         <v>0.0006890000000000001</v>
@@ -50566,7 +50560,7 @@
         <v>-0.39838</v>
       </c>
       <c r="AT41">
-        <v>-14.605992</v>
+        <v>-14.590744</v>
       </c>
     </row>
     <row r="42" spans="1:46">
@@ -50601,7 +50595,7 @@
         <v>723</v>
       </c>
       <c r="K42" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="L42">
         <v>239</v>
@@ -50658,7 +50652,7 @@
         <v>-14.12233333</v>
       </c>
       <c r="AD42" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE42">
         <v>0.002222</v>
@@ -50682,7 +50676,7 @@
         <v>-0.392951</v>
       </c>
       <c r="AL42">
-        <v>-47.444769</v>
+        <v>-47.40234</v>
       </c>
       <c r="AM42">
         <v>0.000678</v>
@@ -50706,7 +50700,7 @@
         <v>-0.392935</v>
       </c>
       <c r="AT42">
-        <v>-14.461173</v>
+        <v>-14.44824</v>
       </c>
     </row>
     <row r="43" spans="1:46">
@@ -50741,7 +50735,7 @@
         <v>724</v>
       </c>
       <c r="K43" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L43">
         <v>135</v>
@@ -50798,7 +50792,7 @@
         <v>-14.26466667</v>
       </c>
       <c r="AD43" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE43">
         <v>-0.015556</v>
@@ -50822,7 +50816,7 @@
         <v>-0.504144</v>
       </c>
       <c r="AL43">
-        <v>-47.10727</v>
+        <v>-47.070438</v>
       </c>
       <c r="AM43">
         <v>-0.004744</v>
@@ -50846,7 +50840,7 @@
         <v>-0.504211</v>
       </c>
       <c r="AT43">
-        <v>-14.358298</v>
+        <v>-14.347071</v>
       </c>
     </row>
     <row r="44" spans="1:46">
@@ -50881,7 +50875,7 @@
         <v>725</v>
       </c>
       <c r="K44" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L44">
         <v>176</v>
@@ -50938,7 +50932,7 @@
         <v>-14.20366667</v>
       </c>
       <c r="AD44" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE44">
         <v>0.006667</v>
@@ -50962,7 +50956,7 @@
         <v>-0.349364</v>
       </c>
       <c r="AL44">
-        <v>-45.942074</v>
+        <v>-45.925315</v>
       </c>
       <c r="AM44">
         <v>0.002033</v>
@@ -50986,7 +50980,7 @@
         <v>-0.349337</v>
       </c>
       <c r="AT44">
-        <v>-14.003147</v>
+        <v>-13.998038</v>
       </c>
     </row>
     <row r="45" spans="1:46">
@@ -51021,7 +51015,7 @@
         <v>726</v>
       </c>
       <c r="K45" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L45">
         <v>20</v>
@@ -51078,7 +51072,7 @@
         <v>-13.89866667</v>
       </c>
       <c r="AD45" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE45">
         <v>0.033333</v>
@@ -51102,7 +51096,7 @@
         <v>-0.16531</v>
       </c>
       <c r="AL45">
-        <v>-45.482069</v>
+        <v>-45.473352</v>
       </c>
       <c r="AM45">
         <v>0.010167</v>
@@ -51126,7 +51120,7 @@
         <v>-0.165155</v>
       </c>
       <c r="AT45">
-        <v>-13.862947</v>
+        <v>-13.860289</v>
       </c>
     </row>
     <row r="46" spans="1:46">
@@ -51161,7 +51155,7 @@
         <v>727</v>
       </c>
       <c r="K46" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L46">
         <v>163</v>
@@ -51218,7 +51212,7 @@
         <v>-13.726</v>
       </c>
       <c r="AD46" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE46">
         <v>0.018889</v>
@@ -51242,7 +51236,7 @@
         <v>-0.26193</v>
       </c>
       <c r="AL46">
-        <v>-45.15099</v>
+        <v>-45.148036</v>
       </c>
       <c r="AM46">
         <v>0.005756</v>
@@ -51266,7 +51260,7 @@
         <v>-0.261963</v>
       </c>
       <c r="AT46">
-        <v>-13.762026</v>
+        <v>-13.761125</v>
       </c>
     </row>
     <row r="47" spans="1:46">
@@ -51301,7 +51295,7 @@
         <v>728</v>
       </c>
       <c r="K47" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="L47">
         <v>150</v>
@@ -51358,7 +51352,7 @@
         <v>-13.03533333</v>
       </c>
       <c r="AD47" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE47">
         <v>0.075556</v>
@@ -51382,7 +51376,7 @@
         <v>0.132399</v>
       </c>
       <c r="AL47">
-        <v>-44.035905</v>
+        <v>-44.051888</v>
       </c>
       <c r="AM47">
         <v>0.023022</v>
@@ -51406,7 +51400,7 @@
         <v>0.132225</v>
       </c>
       <c r="AT47">
-        <v>-13.42214</v>
+        <v>-13.427011</v>
       </c>
     </row>
     <row r="48" spans="1:46">
@@ -51441,7 +51435,7 @@
         <v>729</v>
       </c>
       <c r="K48" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="L48">
         <v>308</v>
@@ -51498,7 +51492,7 @@
         <v>-12.873</v>
       </c>
       <c r="AD48" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE48">
         <v>0.017778</v>
@@ -51522,7 +51516,7 @@
         <v>-0.272583</v>
       </c>
       <c r="AL48">
-        <v>-43.585625</v>
+        <v>-43.608915</v>
       </c>
       <c r="AM48">
         <v>0.005411</v>
@@ -51546,7 +51540,7 @@
         <v>-0.272763</v>
       </c>
       <c r="AT48">
-        <v>-13.284894</v>
+        <v>-13.291993</v>
       </c>
     </row>
     <row r="49" spans="1:46">
@@ -51581,7 +51575,7 @@
         <v>730</v>
       </c>
       <c r="K49" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L49">
         <v>146</v>
@@ -51638,7 +51632,7 @@
         <v>-12.60866667</v>
       </c>
       <c r="AD49" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE49">
         <v>0.028889</v>
@@ -51662,7 +51656,7 @@
         <v>-0.191173</v>
       </c>
       <c r="AL49">
-        <v>-43.285711</v>
+        <v>-43.313719</v>
       </c>
       <c r="AM49">
         <v>0.008810999999999999</v>
@@ -51686,7 +51680,7 @@
         <v>-0.19103</v>
       </c>
       <c r="AT49">
-        <v>-13.19348</v>
+        <v>-13.202017</v>
       </c>
     </row>
     <row r="50" spans="1:46">
@@ -51721,7 +51715,7 @@
         <v>731</v>
       </c>
       <c r="K50" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="L50">
         <v>194</v>
@@ -51778,7 +51772,7 @@
         <v>-12.76066667</v>
       </c>
       <c r="AD50" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE50">
         <v>-0.016667</v>
@@ -51802,7 +51796,7 @@
         <v>-0.513015</v>
       </c>
       <c r="AL50">
-        <v>-42.134147</v>
+        <v>-42.1789</v>
       </c>
       <c r="AM50">
         <v>-0.005067</v>
@@ -51826,7 +51820,7 @@
         <v>-0.512715</v>
       </c>
       <c r="AT50">
-        <v>-12.842493</v>
+        <v>-12.856134</v>
       </c>
     </row>
     <row r="51" spans="1:46">
@@ -51861,7 +51855,7 @@
         <v>732</v>
       </c>
       <c r="K51" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L51">
         <v>65</v>
@@ -51918,7 +51912,7 @@
         <v>-12.75066667</v>
       </c>
       <c r="AD51" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE51">
         <v>0.001111</v>
@@ -51942,7 +51936,7 @@
         <v>-0.379316</v>
       </c>
       <c r="AL51">
-        <v>-41.686281</v>
+        <v>-41.736843</v>
       </c>
       <c r="AM51">
         <v>0.000333</v>
@@ -51966,7 +51960,7 @@
         <v>-0.379462</v>
       </c>
       <c r="AT51">
-        <v>-12.705976</v>
+        <v>-12.721388</v>
       </c>
     </row>
     <row r="52" spans="1:46">
@@ -52001,7 +51995,7 @@
         <v>733</v>
       </c>
       <c r="K52" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="L52">
         <v>120</v>
@@ -52058,7 +52052,7 @@
         <v>-12.446</v>
       </c>
       <c r="AD52" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE52">
         <v>0.033333</v>
@@ -52082,7 +52076,7 @@
         <v>-0.141468</v>
       </c>
       <c r="AL52">
-        <v>-41.434064</v>
+        <v>-41.487696</v>
       </c>
       <c r="AM52">
         <v>0.010156</v>
@@ -52106,7 +52100,7 @@
         <v>-0.141565</v>
       </c>
       <c r="AT52">
-        <v>-12.629095</v>
+        <v>-12.645442</v>
       </c>
     </row>
     <row r="53" spans="1:46">
@@ -52141,7 +52135,7 @@
         <v>734</v>
       </c>
       <c r="K53" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="L53">
         <v>92</v>
@@ -52198,7 +52192,7 @@
         <v>-12.05</v>
       </c>
       <c r="AD53" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE53">
         <v>0.043333</v>
@@ -52222,7 +52216,7 @@
         <v>-0.066703</v>
       </c>
       <c r="AL53">
-        <v>-40.365609</v>
+        <v>-40.430423</v>
       </c>
       <c r="AM53">
         <v>0.0132</v>
@@ -52246,7 +52240,7 @@
         <v>-0.066881</v>
       </c>
       <c r="AT53">
-        <v>-12.303429</v>
+        <v>-12.323185</v>
       </c>
     </row>
     <row r="54" spans="1:46">
@@ -52281,7 +52275,7 @@
         <v>735</v>
       </c>
       <c r="K54" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="L54">
         <v>167</v>
@@ -52338,7 +52332,7 @@
         <v>-11.877</v>
       </c>
       <c r="AD54" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE54">
         <v>0.018889</v>
@@ -52362,7 +52356,7 @@
         <v>-0.247183</v>
       </c>
       <c r="AL54">
-        <v>-39.958858</v>
+        <v>-40.027055</v>
       </c>
       <c r="AM54">
         <v>0.005767</v>
@@ -52386,7 +52380,7 @@
         <v>-0.246938</v>
       </c>
       <c r="AT54">
-        <v>-12.179456</v>
+        <v>-12.200243</v>
       </c>
     </row>
     <row r="55" spans="1:46">
@@ -52421,7 +52415,7 @@
         <v>736</v>
       </c>
       <c r="K55" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L55">
         <v>47</v>
@@ -52478,7 +52472,7 @@
         <v>-12.01933333</v>
       </c>
       <c r="AD55" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE55">
         <v>-0.015556</v>
@@ -52502,7 +52496,7 @@
         <v>-0.501488</v>
       </c>
       <c r="AL55">
-        <v>-39.697548</v>
+        <v>-39.767635</v>
       </c>
       <c r="AM55">
         <v>-0.004744</v>
@@ -52526,7 +52520,7 @@
         <v>-0.501561</v>
       </c>
       <c r="AT55">
-        <v>-12.0998</v>
+        <v>-12.121163</v>
       </c>
     </row>
     <row r="56" spans="1:46">
@@ -52561,7 +52555,7 @@
         <v>737</v>
       </c>
       <c r="K56" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="L56">
         <v>242</v>
@@ -52618,7 +52612,7 @@
         <v>-11.53166667</v>
       </c>
       <c r="AD56" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE56">
         <v>0.053333</v>
@@ -52642,7 +52636,7 @@
         <v>0.022613</v>
       </c>
       <c r="AL56">
-        <v>-38.756319</v>
+        <v>-38.831165</v>
       </c>
       <c r="AM56">
         <v>0.016256</v>
@@ -52666,7 +52660,7 @@
         <v>0.022613</v>
       </c>
       <c r="AT56">
-        <v>-11.812913</v>
+        <v>-11.835726</v>
       </c>
     </row>
     <row r="57" spans="1:46">
@@ -52701,7 +52695,7 @@
         <v>738</v>
       </c>
       <c r="K57" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L57">
         <v>81</v>
@@ -52758,7 +52752,7 @@
         <v>-11.52133333</v>
       </c>
       <c r="AD57" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE57">
         <v>0.001111</v>
@@ -52782,7 +52776,7 @@
         <v>-0.37476</v>
       </c>
       <c r="AL57">
-        <v>-38.379443</v>
+        <v>-38.455197</v>
       </c>
       <c r="AM57">
         <v>0.000344</v>
@@ -52806,7 +52800,7 @@
         <v>-0.374638</v>
       </c>
       <c r="AT57">
-        <v>-11.698053</v>
+        <v>-11.721143</v>
       </c>
     </row>
     <row r="58" spans="1:46">
@@ -52841,7 +52835,7 @@
         <v>739</v>
       </c>
       <c r="K58" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="L58">
         <v>162</v>
@@ -52898,7 +52892,7 @@
         <v>-11.39933333</v>
       </c>
       <c r="AD58" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE58">
         <v>0.013333</v>
@@ -52922,7 +52916,7 @@
         <v>-0.277426</v>
       </c>
       <c r="AL58">
-        <v>-38.154111</v>
+        <v>-38.230104</v>
       </c>
       <c r="AM58">
         <v>0.004067</v>
@@ -52946,7 +52940,7 @@
         <v>-0.277352</v>
       </c>
       <c r="AT58">
-        <v>-11.629366</v>
+        <v>-11.652529</v>
       </c>
     </row>
     <row r="59" spans="1:46">
@@ -52981,7 +52975,7 @@
         <v>740</v>
       </c>
       <c r="K59" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="L59">
         <v>154</v>
@@ -53038,7 +53032,7 @@
         <v>-11.61266667</v>
       </c>
       <c r="AD59" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE59">
         <v>-0.023333</v>
@@ -53062,7 +53056,7 @@
         <v>-0.557385</v>
       </c>
       <c r="AL59">
-        <v>-37.271517</v>
+        <v>-37.346019</v>
       </c>
       <c r="AM59">
         <v>-0.007111</v>
@@ -53086,7 +53080,7 @@
         <v>-0.557378</v>
       </c>
       <c r="AT59">
-        <v>-11.360352</v>
+        <v>-11.383061</v>
       </c>
     </row>
     <row r="60" spans="1:46">
@@ -53121,7 +53115,7 @@
         <v>741</v>
       </c>
       <c r="K60" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L60">
         <v>198</v>
@@ -53178,7 +53172,7 @@
         <v>-11.542</v>
       </c>
       <c r="AD60" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE60">
         <v>0.007778</v>
@@ -53202,7 +53196,7 @@
         <v>-0.309931</v>
       </c>
       <c r="AL60">
-        <v>-36.943319</v>
+        <v>-37.016163</v>
       </c>
       <c r="AM60">
         <v>0.002356</v>
@@ -53226,7 +53220,7 @@
         <v>-0.31032</v>
       </c>
       <c r="AT60">
-        <v>-11.260312</v>
+        <v>-11.282515</v>
       </c>
     </row>
     <row r="61" spans="1:46">
@@ -53261,7 +53255,7 @@
         <v>742</v>
       </c>
       <c r="K61" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L61">
         <v>106</v>
@@ -53318,7 +53312,7 @@
         <v>-11.44033333</v>
       </c>
       <c r="AD61" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE61">
         <v>0.011111</v>
@@ -53342,7 +53336,7 @@
         <v>-0.280954</v>
       </c>
       <c r="AL61">
-        <v>-36.755244</v>
+        <v>-36.826836</v>
       </c>
       <c r="AM61">
         <v>0.003389</v>
@@ -53366,7 +53360,7 @@
         <v>-0.2809</v>
       </c>
       <c r="AT61">
-        <v>-11.202984</v>
+        <v>-11.224806</v>
       </c>
     </row>
     <row r="62" spans="1:46">
@@ -53401,7 +53395,7 @@
         <v>743</v>
       </c>
       <c r="K62" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L62">
         <v>70</v>
@@ -53458,7 +53452,7 @@
         <v>-11.13533333</v>
       </c>
       <c r="AD62" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE62">
         <v>0.033333</v>
@@ -53482,7 +53476,7 @@
         <v>-0.102614</v>
       </c>
       <c r="AL62">
-        <v>-36.016203</v>
+        <v>-36.080497</v>
       </c>
       <c r="AM62">
         <v>0.010167</v>
@@ -53506,7 +53500,7 @@
         <v>-0.102426</v>
       </c>
       <c r="AT62">
-        <v>-10.977732</v>
+        <v>-10.99733</v>
       </c>
     </row>
     <row r="63" spans="1:46">
@@ -53541,7 +53535,7 @@
         <v>744</v>
       </c>
       <c r="K63" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="L63">
         <v>161</v>
@@ -53598,7 +53592,7 @@
         <v>-11.22666667</v>
       </c>
       <c r="AD63" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE63">
         <v>-0.01</v>
@@ -53622,7 +53616,7 @@
         <v>-0.447225</v>
       </c>
       <c r="AL63">
-        <v>-35.563968</v>
+        <v>-35.621655</v>
       </c>
       <c r="AM63">
         <v>-0.003044</v>
@@ -53646,7 +53640,7 @@
         <v>-0.447125</v>
       </c>
       <c r="AT63">
-        <v>-10.839888</v>
+        <v>-10.857471</v>
       </c>
     </row>
     <row r="64" spans="1:46">
@@ -53681,7 +53675,7 @@
         <v>745</v>
       </c>
       <c r="K64" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="L64">
         <v>169</v>
@@ -53738,7 +53732,7 @@
         <v>-11.044</v>
       </c>
       <c r="AD64" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE64">
         <v>0.02</v>
@@ -53762,7 +53756,7 @@
         <v>-0.202269</v>
       </c>
       <c r="AL64">
-        <v>-34.959318</v>
+        <v>-35.0051</v>
       </c>
       <c r="AM64">
         <v>0.006089</v>
@@ -53786,7 +53780,7 @@
         <v>-0.202456</v>
       </c>
       <c r="AT64">
-        <v>-10.655591</v>
+        <v>-10.669546</v>
       </c>
     </row>
     <row r="65" spans="1:46">
@@ -53821,7 +53815,7 @@
         <v>746</v>
       </c>
       <c r="K65" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="L65">
         <v>129</v>
@@ -53878,7 +53872,7 @@
         <v>-10.64766667</v>
       </c>
       <c r="AD65" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE65">
         <v>0.043333</v>
@@ -53902,7 +53896,7 @@
         <v>-0.011478</v>
       </c>
       <c r="AL65">
-        <v>-34.618157</v>
+        <v>-34.655388</v>
       </c>
       <c r="AM65">
         <v>0.013211</v>
@@ -53926,7 +53920,7 @@
         <v>-0.011381</v>
       </c>
       <c r="AT65">
-        <v>-10.551605</v>
+        <v>-10.562954</v>
       </c>
     </row>
     <row r="66" spans="1:46">
@@ -53961,7 +53955,7 @@
         <v>747</v>
       </c>
       <c r="K66" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="L66">
         <v>165</v>
@@ -54018,7 +54012,7 @@
         <v>-10.51566667</v>
       </c>
       <c r="AD66" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE66">
         <v>0.014444</v>
@@ -54042,7 +54036,7 @@
         <v>-0.247472</v>
       </c>
       <c r="AL66">
-        <v>-34.135069</v>
+        <v>-34.157459</v>
       </c>
       <c r="AM66">
         <v>0.0044</v>
@@ -54066,7 +54060,7 @@
         <v>-0.247535</v>
       </c>
       <c r="AT66">
-        <v>-10.404359</v>
+        <v>-10.411184</v>
       </c>
     </row>
     <row r="67" spans="1:46">
@@ -54101,7 +54095,7 @@
         <v>748</v>
       </c>
       <c r="K67" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="L67">
         <v>158</v>
@@ -54158,7 +54152,7 @@
         <v>-10.817</v>
       </c>
       <c r="AD67" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE67">
         <v>-0.010988</v>
@@ -54182,7 +54176,7 @@
         <v>-0.454375</v>
       </c>
       <c r="AL67">
-        <v>-33.963438</v>
+        <v>-33.979669</v>
       </c>
       <c r="AM67">
         <v>-0.003348</v>
@@ -54206,7 +54200,7 @@
         <v>-0.454339</v>
       </c>
       <c r="AT67">
-        <v>-10.352047</v>
+        <v>-10.356994</v>
       </c>
     </row>
     <row r="68" spans="1:46">
@@ -54241,7 +54235,7 @@
         <v>749</v>
       </c>
       <c r="K68" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="L68">
         <v>138</v>
@@ -54298,7 +54292,7 @@
         <v>-10.46466667</v>
       </c>
       <c r="AD68" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE68">
         <v>0.038519</v>
@@ -54322,7 +54316,7 @@
         <v>-0.040494</v>
       </c>
       <c r="AL68">
-        <v>-33.864961</v>
+        <v>-33.877425</v>
       </c>
       <c r="AM68">
         <v>0.011744</v>
@@ -54346,7 +54340,7 @@
         <v>-0.04041</v>
       </c>
       <c r="AT68">
-        <v>-10.322035</v>
+        <v>-10.325834</v>
       </c>
     </row>
     <row r="69" spans="1:46">
@@ -54381,7 +54375,7 @@
         <v>750</v>
       </c>
       <c r="K69" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="L69">
         <v>169</v>
@@ -54438,7 +54432,7 @@
         <v>-10.37333333</v>
       </c>
       <c r="AD69" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE69">
         <v>0.01</v>
@@ -54462,7 +54456,7 @@
         <v>-0.278349</v>
       </c>
       <c r="AL69">
-        <v>-33.488885</v>
+        <v>-33.485244</v>
       </c>
       <c r="AM69">
         <v>0.003044</v>
@@ -54486,7 +54480,7 @@
         <v>-0.27847</v>
       </c>
       <c r="AT69">
-        <v>-10.207405</v>
+        <v>-10.206295</v>
       </c>
     </row>
     <row r="70" spans="1:46">
@@ -54521,7 +54515,7 @@
         <v>751</v>
       </c>
       <c r="K70" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="L70">
         <v>132</v>
@@ -54578,7 +54572,7 @@
         <v>-10.38333333</v>
       </c>
       <c r="AD70" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE70">
         <v>-0.001111</v>
@@ -54602,7 +54596,7 @@
         <v>-0.369461</v>
       </c>
       <c r="AL70">
-        <v>-33.354378</v>
+        <v>-33.344267</v>
       </c>
       <c r="AM70">
         <v>-0.000333</v>
@@ -54626,7 +54620,7 @@
         <v>-0.36931</v>
       </c>
       <c r="AT70">
-        <v>-10.16641</v>
+        <v>-10.163328</v>
       </c>
     </row>
     <row r="71" spans="1:46">
@@ -54661,7 +54655,7 @@
         <v>752</v>
       </c>
       <c r="K71" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="L71">
         <v>150</v>
@@ -54718,7 +54712,7 @@
         <v>-10.526</v>
       </c>
       <c r="AD71" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE71">
         <v>-0.015556</v>
@@ -54742,7 +54736,7 @@
         <v>-0.488321</v>
       </c>
       <c r="AL71">
-        <v>-33.270841</v>
+        <v>-33.256514</v>
       </c>
       <c r="AM71">
         <v>-0.004756</v>
@@ -54766,7 +54760,7 @@
         <v>-0.488738</v>
       </c>
       <c r="AT71">
-        <v>-10.140944</v>
+        <v>-10.136577</v>
       </c>
     </row>
     <row r="72" spans="1:46">
@@ -54801,7 +54795,7 @@
         <v>753</v>
       </c>
       <c r="K72" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="L72">
         <v>132</v>
@@ -54858,7 +54852,7 @@
         <v>-10.55633333</v>
       </c>
       <c r="AD72" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE72">
         <v>-0.003333</v>
@@ -54882,7 +54876,7 @@
         <v>-0.38032</v>
       </c>
       <c r="AL72">
-        <v>-32.980266</v>
+        <v>-32.95011</v>
       </c>
       <c r="AM72">
         <v>-0.001011</v>
@@ -54906,7 +54900,7 @@
         <v>-0.380174</v>
       </c>
       <c r="AT72">
-        <v>-10.052378</v>
+        <v>-10.043186</v>
       </c>
     </row>
     <row r="73" spans="1:46">
@@ -54941,7 +54935,7 @@
         <v>754</v>
       </c>
       <c r="K73" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="L73">
         <v>152</v>
@@ -54998,7 +54992,7 @@
         <v>-10.414</v>
       </c>
       <c r="AD73" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE73">
         <v>0.015556</v>
@@ -55022,7 +55016,7 @@
         <v>-0.215626</v>
       </c>
       <c r="AL73">
-        <v>-32.818492</v>
+        <v>-32.778834</v>
       </c>
       <c r="AM73">
         <v>0.004744</v>
@@ -55046,7 +55040,7 @@
         <v>-0.215541</v>
       </c>
       <c r="AT73">
-        <v>-10.00307</v>
+        <v>-9.990983</v>
       </c>
     </row>
     <row r="74" spans="1:46">
@@ -55081,7 +55075,7 @@
         <v>755</v>
       </c>
       <c r="K74" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L74">
         <v>131</v>
@@ -55138,7 +55132,7 @@
         <v>-10.28166667</v>
       </c>
       <c r="AD74" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE74">
         <v>0.014444</v>
@@ -55162,7 +55156,7 @@
         <v>-0.223666</v>
       </c>
       <c r="AL74">
-        <v>-32.59725</v>
+        <v>-32.544234</v>
       </c>
       <c r="AM74">
         <v>0.004411</v>
@@ -55186,7 +55180,7 @@
         <v>-0.223435</v>
       </c>
       <c r="AT74">
-        <v>-9.935639999999999</v>
+        <v>-9.91948</v>
       </c>
     </row>
     <row r="75" spans="1:46">
@@ -55221,7 +55215,7 @@
         <v>756</v>
       </c>
       <c r="K75" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L75">
         <v>126</v>
@@ -55278,7 +55272,7 @@
         <v>-10.292</v>
       </c>
       <c r="AD75" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE75">
         <v>-0.001111</v>
@@ -55302,7 +55296,7 @@
         <v>-0.357065</v>
       </c>
       <c r="AL75">
-        <v>-32.468113</v>
+        <v>-32.407505</v>
       </c>
       <c r="AM75">
         <v>-0.000344</v>
@@ -55326,7 +55320,7 @@
         <v>-0.357219</v>
       </c>
       <c r="AT75">
-        <v>-9.896278000000001</v>
+        <v>-9.877803999999999</v>
       </c>
     </row>
     <row r="76" spans="1:46">
@@ -55361,7 +55355,7 @@
         <v>757</v>
       </c>
       <c r="K76" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="L76">
         <v>141</v>
@@ -55418,7 +55412,7 @@
         <v>-10.282</v>
       </c>
       <c r="AD76" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE76">
         <v>0.001111</v>
@@ -55442,7 +55436,7 @@
         <v>-0.334979</v>
       </c>
       <c r="AL76">
-        <v>-32.28507</v>
+        <v>-32.214864</v>
       </c>
       <c r="AM76">
         <v>0.000333</v>
@@ -55466,7 +55460,7 @@
         <v>-0.335136</v>
       </c>
       <c r="AT76">
-        <v>-9.840488000000001</v>
+        <v>-9.819089</v>
       </c>
     </row>
     <row r="77" spans="1:46">
@@ -55501,7 +55495,7 @@
         <v>758</v>
       </c>
       <c r="K77" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="L77">
         <v>119</v>
@@ -55558,7 +55552,7 @@
         <v>-10.34288889</v>
       </c>
       <c r="AD77" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE77">
         <v>-0.002222</v>
@@ -55582,7 +55576,7 @@
         <v>-0.361776</v>
       </c>
       <c r="AL77">
-        <v>-32.216612</v>
+        <v>-32.143417</v>
       </c>
       <c r="AM77">
         <v>-0.000677</v>
@@ -55606,7 +55600,7 @@
         <v>-0.361778</v>
       </c>
       <c r="AT77">
-        <v>-9.819623</v>
+        <v>-9.797313000000001</v>
       </c>
     </row>
     <row r="78" spans="1:46">
@@ -55641,7 +55635,7 @@
         <v>759</v>
       </c>
       <c r="K78" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="L78">
         <v>142</v>
@@ -55698,7 +55692,7 @@
         <v>-9.967000000000001</v>
       </c>
       <c r="AD78" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE78">
         <v>0.041111</v>
@@ -55722,7 +55716,7 @@
         <v>0.024309</v>
       </c>
       <c r="AL78">
-        <v>-32.180501</v>
+        <v>-32.105903</v>
       </c>
       <c r="AM78">
         <v>0.01253</v>
@@ -55746,7 +55740,7 @@
         <v>0.024288</v>
       </c>
       <c r="AT78">
-        <v>-9.808615</v>
+        <v>-9.785876999999999</v>
       </c>
     </row>
     <row r="79" spans="1:46">
@@ -55781,7 +55775,7 @@
         <v>760</v>
       </c>
       <c r="K79" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="L79">
         <v>129</v>
@@ -55838,7 +55832,7 @@
         <v>-9.784000000000001</v>
       </c>
       <c r="AD79" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE79">
         <v>0.02</v>
@@ -55862,7 +55856,7 @@
         <v>-0.164046</v>
       </c>
       <c r="AL79">
-        <v>-32.013268</v>
+        <v>-31.933995</v>
       </c>
       <c r="AM79">
         <v>0.0061</v>
@@ -55886,7 +55880,7 @@
         <v>-0.163916</v>
       </c>
       <c r="AT79">
-        <v>-9.757645</v>
+        <v>-9.733482</v>
       </c>
     </row>
     <row r="80" spans="1:46">
@@ -55921,7 +55915,7 @@
         <v>761</v>
       </c>
       <c r="K80" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="L80">
         <v>152</v>
@@ -55978,7 +55972,7 @@
         <v>-9.702999999999999</v>
       </c>
       <c r="AD80" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE80">
         <v>0.008888999999999999</v>
@@ -56002,7 +55996,7 @@
         <v>-0.262589</v>
       </c>
       <c r="AL80">
-        <v>-31.947027</v>
+        <v>-31.866792</v>
       </c>
       <c r="AM80">
         <v>0.0027</v>
@@ -56026,7 +56020,7 @@
         <v>-0.262879</v>
       </c>
       <c r="AT80">
-        <v>-9.737454</v>
+        <v>-9.712997</v>
       </c>
     </row>
     <row r="81" spans="1:46">
@@ -56061,7 +56055,7 @@
         <v>762</v>
       </c>
       <c r="K81" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="L81">
         <v>129</v>
@@ -56118,7 +56112,7 @@
         <v>-9.773999999999999</v>
       </c>
       <c r="AD81" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE81">
         <v>-0.007778</v>
@@ -56142,7 +56136,7 @@
         <v>-0.410986</v>
       </c>
       <c r="AL81">
-        <v>-31.907879</v>
+        <v>-31.827315</v>
       </c>
       <c r="AM81">
         <v>-0.002367</v>
@@ -56166,7 +56160,7 @@
         <v>-0.41088</v>
       </c>
       <c r="AT81">
-        <v>-9.725521000000001</v>
+        <v>-9.700965</v>
       </c>
     </row>
     <row r="82" spans="1:46">
@@ -56201,7 +56195,7 @@
         <v>763</v>
       </c>
       <c r="K82" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L82">
         <v>136</v>
@@ -56258,7 +56252,7 @@
         <v>-9.62166667</v>
       </c>
       <c r="AD82" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE82">
         <v>0.016667</v>
@@ -56282,7 +56276,7 @@
         <v>-0.186479</v>
       </c>
       <c r="AL82">
-        <v>-31.732012</v>
+        <v>-31.652003</v>
       </c>
       <c r="AM82">
         <v>0.005078</v>
@@ -56306,7 +56300,7 @@
         <v>-0.18655</v>
       </c>
       <c r="AT82">
-        <v>-9.671919000000001</v>
+        <v>-9.647531000000001</v>
       </c>
     </row>
     <row r="83" spans="1:46">
@@ -56341,7 +56335,7 @@
         <v>764</v>
       </c>
       <c r="K83" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L83">
         <v>122</v>
@@ -56398,7 +56392,7 @@
         <v>-9.57066667</v>
       </c>
       <c r="AD83" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE83">
         <v>0.005556</v>
@@ -56422,7 +56416,7 @@
         <v>-0.28669</v>
       </c>
       <c r="AL83">
-        <v>-31.658686</v>
+        <v>-31.579771</v>
       </c>
       <c r="AM83">
         <v>0.0017</v>
@@ -56446,7 +56440,7 @@
         <v>-0.286503</v>
       </c>
       <c r="AT83">
-        <v>-9.649569</v>
+        <v>-9.625515</v>
       </c>
     </row>
     <row r="84" spans="1:46">
@@ -56481,7 +56475,7 @@
         <v>765</v>
       </c>
       <c r="K84" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L84">
         <v>144</v>
@@ -56538,7 +56532,7 @@
         <v>-9.428333329999999</v>
       </c>
       <c r="AD84" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE84">
         <v>0.015556</v>
@@ -56562,7 +56556,7 @@
         <v>-0.193025</v>
       </c>
       <c r="AL84">
-        <v>-31.618329</v>
+        <v>-31.5402</v>
       </c>
       <c r="AM84">
         <v>0.004744</v>
@@ -56586,7 +56580,7 @@
         <v>-0.192964</v>
       </c>
       <c r="AT84">
-        <v>-9.637269</v>
+        <v>-9.613454000000001</v>
       </c>
     </row>
     <row r="85" spans="1:46">
@@ -56621,7 +56615,7 @@
         <v>766</v>
       </c>
       <c r="K85" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="L85">
         <v>130</v>
@@ -56678,7 +56672,7 @@
         <v>-9.29633333</v>
       </c>
       <c r="AD85" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE85">
         <v>0.014444</v>
@@ -56702,7 +56696,7 @@
         <v>-0.202097</v>
       </c>
       <c r="AL85">
-        <v>-31.41547</v>
+        <v>-31.34287</v>
       </c>
       <c r="AM85">
         <v>0.0044</v>
@@ -56726,7 +56720,7 @@
         <v>-0.202173</v>
       </c>
       <c r="AT85">
-        <v>-9.575438</v>
+        <v>-9.553309</v>
       </c>
     </row>
     <row r="86" spans="1:46">
@@ -56761,7 +56755,7 @@
         <v>767</v>
       </c>
       <c r="K86" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="L86">
         <v>155</v>
@@ -56818,7 +56812,7 @@
         <v>-9.215</v>
       </c>
       <c r="AD86" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE86">
         <v>0.008888999999999999</v>
@@ -56842,7 +56836,7 @@
         <v>-0.252472</v>
       </c>
       <c r="AL86">
-        <v>-31.33026</v>
+        <v>-31.260594</v>
       </c>
       <c r="AM86">
         <v>0.002711</v>
@@ -56866,7 +56860,7 @@
         <v>-0.252431</v>
       </c>
       <c r="AT86">
-        <v>-9.549467</v>
+        <v>-9.528231999999999</v>
       </c>
     </row>
     <row r="87" spans="1:46">
@@ -56901,7 +56895,7 @@
         <v>768</v>
       </c>
       <c r="K87" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="L87">
         <v>161</v>
@@ -56958,7 +56952,7 @@
         <v>-9.154</v>
       </c>
       <c r="AD87" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE87">
         <v>0.006667</v>
@@ -56982,7 +56976,7 @@
         <v>-0.27166</v>
       </c>
       <c r="AL87">
-        <v>-31.283827</v>
+        <v>-31.215873</v>
       </c>
       <c r="AM87">
         <v>0.002033</v>
@@ -57006,7 +57000,7 @@
         <v>-0.271627</v>
       </c>
       <c r="AT87">
-        <v>-9.535315000000001</v>
+        <v>-9.514602</v>
       </c>
     </row>
     <row r="88" spans="1:46">
@@ -57041,7 +57035,7 @@
         <v>769</v>
       </c>
       <c r="K88" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="L88">
         <v>141</v>
@@ -57098,7 +57092,7 @@
         <v>-8.941000000000001</v>
       </c>
       <c r="AD88" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE88">
         <v>0.023333</v>
@@ -57122,7 +57116,7 @@
         <v>-0.113326</v>
       </c>
       <c r="AL88">
-        <v>-31.046273</v>
+        <v>-30.987991</v>
       </c>
       <c r="AM88">
         <v>0.0071</v>
@@ -57146,7 +57140,7 @@
         <v>-0.113706</v>
       </c>
       <c r="AT88">
-        <v>-9.462904999999999</v>
+        <v>-9.445141</v>
       </c>
     </row>
     <row r="89" spans="1:46">
@@ -57181,7 +57175,7 @@
         <v>770</v>
       </c>
       <c r="K89" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="L89">
         <v>161</v>
@@ -57238,7 +57232,7 @@
         <v>-8.60566667</v>
       </c>
       <c r="AD89" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE89">
         <v>0.036667</v>
@@ -57262,7 +57256,7 @@
         <v>0.013487</v>
       </c>
       <c r="AL89">
-        <v>-30.958518</v>
+        <v>-30.904082</v>
       </c>
       <c r="AM89">
         <v>0.011178</v>
@@ -57286,7 +57280,7 @@
         <v>0.013535</v>
       </c>
       <c r="AT89">
-        <v>-9.436159</v>
+        <v>-9.419566</v>
       </c>
     </row>
     <row r="90" spans="1:46">
@@ -57321,7 +57315,7 @@
         <v>771</v>
       </c>
       <c r="K90" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="L90">
         <v>150</v>
@@ -57378,7 +57372,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="AD90" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE90">
         <v>-0.028889</v>
@@ -57402,7 +57396,7 @@
         <v>-0.609226</v>
       </c>
       <c r="AL90">
-        <v>-30.889571</v>
+        <v>-30.838223</v>
       </c>
       <c r="AM90">
         <v>-0.008810999999999999</v>
@@ -57426,7 +57420,7 @@
         <v>-0.609399</v>
       </c>
       <c r="AT90">
-        <v>-9.415141999999999</v>
+        <v>-9.399490999999999</v>
       </c>
     </row>
     <row r="91" spans="1:46">
@@ -57461,7 +57455,7 @@
         <v>772</v>
       </c>
       <c r="K91" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="L91">
         <v>162</v>
@@ -57518,7 +57512,7 @@
         <v>-9.032</v>
       </c>
       <c r="AD91" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE91">
         <v>-0.017778</v>
@@ -57542,7 +57536,7 @@
         <v>-0.498982</v>
       </c>
       <c r="AL91">
-        <v>-30.593337</v>
+        <v>-30.555648</v>
       </c>
       <c r="AM91">
         <v>-0.0054</v>
@@ -57566,7 +57560,7 @@
         <v>-0.49837</v>
       </c>
       <c r="AT91">
-        <v>-9.324854</v>
+        <v>-9.313366</v>
       </c>
     </row>
     <row r="92" spans="1:46">
@@ -57601,7 +57595,7 @@
         <v>773</v>
       </c>
       <c r="K92" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="L92">
         <v>168</v>
@@ -57658,7 +57652,7 @@
         <v>-8.940666670000001</v>
       </c>
       <c r="AD92" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE92">
         <v>0.01</v>
@@ -57682,7 +57676,7 @@
         <v>-0.229646</v>
       </c>
       <c r="AL92">
-        <v>-30.492805</v>
+        <v>-30.459815</v>
       </c>
       <c r="AM92">
         <v>0.003044</v>
@@ -57706,7 +57700,7 @@
         <v>-0.229761</v>
       </c>
       <c r="AT92">
-        <v>-9.294212</v>
+        <v>-9.284155999999999</v>
       </c>
     </row>
     <row r="93" spans="1:46">
@@ -57741,7 +57735,7 @@
         <v>774</v>
       </c>
       <c r="K93" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="L93">
         <v>141</v>
@@ -57798,7 +57792,7 @@
         <v>-8.92033333</v>
       </c>
       <c r="AD93" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE93">
         <v>0.002222</v>
@@ -57822,7 +57816,7 @@
         <v>-0.303265</v>
       </c>
       <c r="AL93">
-        <v>-30.411406</v>
+        <v>-30.382221</v>
       </c>
       <c r="AM93">
         <v>0.000678</v>
@@ -57846,7 +57840,7 @@
         <v>-0.303246</v>
       </c>
       <c r="AT93">
-        <v>-9.269399999999999</v>
+        <v>-9.260503999999999</v>
       </c>
     </row>
     <row r="94" spans="1:46">
@@ -57881,7 +57875,7 @@
         <v>775</v>
       </c>
       <c r="K94" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="L94">
         <v>174</v>
@@ -57938,7 +57932,7 @@
         <v>-8.514333329999999</v>
       </c>
       <c r="AD94" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE94">
         <v>0.044444</v>
@@ -57962,7 +57956,7 @@
         <v>0.107755</v>
       </c>
       <c r="AL94">
-        <v>-30.086561</v>
+        <v>-30.072422</v>
       </c>
       <c r="AM94">
         <v>0.013533</v>
@@ -57986,7 +57980,7 @@
         <v>0.107316</v>
       </c>
       <c r="AT94">
-        <v>-9.170384</v>
+        <v>-9.166074999999999</v>
       </c>
     </row>
     <row r="95" spans="1:46">
@@ -58021,7 +58015,7 @@
         <v>776</v>
       </c>
       <c r="K95" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="L95">
         <v>168</v>
@@ -58078,7 +58072,7 @@
         <v>-8.625666669999999</v>
       </c>
       <c r="AD95" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE95">
         <v>-0.012222</v>
@@ -58102,7 +58096,7 @@
         <v>-0.444823</v>
       </c>
       <c r="AL95">
-        <v>-29.867953</v>
+        <v>-29.863692</v>
       </c>
       <c r="AM95">
         <v>-0.003711</v>
@@ -58126,7 +58120,7 @@
         <v>-0.444362</v>
       </c>
       <c r="AT95">
-        <v>-9.103759</v>
+        <v>-9.102460000000001</v>
       </c>
     </row>
     <row r="96" spans="1:46">
@@ -58161,7 +58155,7 @@
         <v>777</v>
       </c>
       <c r="K96" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="L96">
         <v>140</v>
@@ -58218,7 +58212,7 @@
         <v>-8.829000000000001</v>
       </c>
       <c r="AD96" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE96">
         <v>-0.022222</v>
@@ -58242,7 +58236,7 @@
         <v>-0.539551</v>
       </c>
       <c r="AL96">
-        <v>-29.481342</v>
+        <v>-29.493834</v>
       </c>
       <c r="AM96">
         <v>-0.006778</v>
@@ -58266,7 +58260,7 @@
         <v>-0.539704</v>
       </c>
       <c r="AT96">
-        <v>-8.985913999999999</v>
+        <v>-8.989720999999999</v>
       </c>
     </row>
     <row r="97" spans="1:46">
@@ -58301,7 +58295,7 @@
         <v>778</v>
       </c>
       <c r="K97" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="L97">
         <v>166</v>
@@ -58358,7 +58352,7 @@
         <v>-8.859500000000001</v>
       </c>
       <c r="AD97" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE97">
         <v>-0.001667</v>
@@ -58382,7 +58376,7 @@
         <v>-0.334445</v>
       </c>
       <c r="AL97">
-        <v>-29.320907</v>
+        <v>-29.340032</v>
       </c>
       <c r="AM97">
         <v>-0.000508</v>
@@ -58406,7 +58400,7 @@
         <v>-0.334452</v>
       </c>
       <c r="AT97">
-        <v>-8.937018</v>
+        <v>-8.942847</v>
       </c>
     </row>
     <row r="98" spans="1:46">
@@ -58441,7 +58435,7 @@
         <v>779</v>
       </c>
       <c r="K98" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="L98">
         <v>155</v>
@@ -58498,7 +58492,7 @@
         <v>-8.819000000000001</v>
       </c>
       <c r="AD98" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE98">
         <v>0.004444</v>
@@ -58522,7 +58516,7 @@
         <v>-0.272245</v>
       </c>
       <c r="AL98">
-        <v>-29.235305</v>
+        <v>-29.257885</v>
       </c>
       <c r="AM98">
         <v>0.00135</v>
@@ -58546,7 +58540,7 @@
         <v>-0.272385</v>
       </c>
       <c r="AT98">
-        <v>-8.910925000000001</v>
+        <v>-8.917807</v>
       </c>
     </row>
     <row r="99" spans="1:46">
@@ -58581,7 +58575,7 @@
         <v>780</v>
       </c>
       <c r="K99" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="L99">
         <v>169</v>
@@ -58638,7 +58632,7 @@
         <v>-8.656333330000001</v>
       </c>
       <c r="AD99" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE99">
         <v>0.017778</v>
@@ -58662,7 +58656,7 @@
         <v>-0.138464</v>
       </c>
       <c r="AL99">
-        <v>-28.8196</v>
+        <v>-28.85806</v>
       </c>
       <c r="AM99">
         <v>0.005422</v>
@@ -58686,7 +58680,7 @@
         <v>-0.138377</v>
       </c>
       <c r="AT99">
-        <v>-8.784212999999999</v>
+        <v>-8.795935999999999</v>
       </c>
     </row>
     <row r="100" spans="1:46">
@@ -58721,7 +58715,7 @@
         <v>781</v>
       </c>
       <c r="K100" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="L100">
         <v>141</v>
@@ -58778,7 +58772,7 @@
         <v>-8.707333330000001</v>
       </c>
       <c r="AD100" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE100">
         <v>-0.005556</v>
@@ -58802,7 +58796,7 @@
         <v>-0.370352</v>
       </c>
       <c r="AL100">
-        <v>-28.640608</v>
+        <v>-28.685418</v>
       </c>
       <c r="AM100">
         <v>-0.0017</v>
@@ -58826,7 +58820,7 @@
         <v>-0.370575</v>
       </c>
       <c r="AT100">
-        <v>-8.729657</v>
+        <v>-8.743316</v>
       </c>
     </row>
     <row r="101" spans="1:46">
@@ -58861,7 +58855,7 @@
         <v>782</v>
       </c>
       <c r="K101" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="L101">
         <v>144</v>
@@ -58918,7 +58912,7 @@
         <v>-8.635999999999999</v>
       </c>
       <c r="AD101" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE101">
         <v>0.007778</v>
@@ -58942,7 +58936,7 @@
         <v>-0.234771</v>
       </c>
       <c r="AL101">
-        <v>-28.553726</v>
+        <v>-28.601505</v>
       </c>
       <c r="AM101">
         <v>0.002378</v>
@@ -58966,7 +58960,7 @@
         <v>-0.23453</v>
       </c>
       <c r="AT101">
-        <v>-8.703179</v>
+        <v>-8.717741999999999</v>
       </c>
     </row>
     <row r="102" spans="1:46">
@@ -59001,7 +58995,7 @@
         <v>783</v>
       </c>
       <c r="K102" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="L102">
         <v>155</v>
@@ -59058,7 +59052,7 @@
         <v>-8.839</v>
       </c>
       <c r="AD102" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE102">
         <v>-0.022222</v>
@@ -59082,7 +59076,7 @@
         <v>-0.5350279999999999</v>
       </c>
       <c r="AL102">
-        <v>-28.092817</v>
+        <v>-28.155058</v>
       </c>
       <c r="AM102">
         <v>-0.006767</v>
@@ -59106,7 +59100,7 @@
         <v>-0.534836</v>
       </c>
       <c r="AT102">
-        <v>-8.562694</v>
+        <v>-8.581664999999999</v>
       </c>
     </row>
     <row r="103" spans="1:46">
@@ -59141,7 +59135,7 @@
         <v>784</v>
       </c>
       <c r="K103" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="L103">
         <v>160</v>
@@ -59198,7 +59192,7 @@
         <v>-8.72733333</v>
       </c>
       <c r="AD103" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE103">
         <v>0.012222</v>
@@ -59222,7 +59216,7 @@
         <v>-0.184126</v>
       </c>
       <c r="AL103">
-        <v>-27.914144</v>
+        <v>-27.981373</v>
       </c>
       <c r="AM103">
         <v>0.003722</v>
@@ -59246,7 +59240,7 @@
         <v>-0.184236</v>
       </c>
       <c r="AT103">
-        <v>-8.508233000000001</v>
+        <v>-8.528724</v>
       </c>
     </row>
     <row r="104" spans="1:46">
@@ -59281,7 +59275,7 @@
         <v>785</v>
       </c>
       <c r="K104" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="L104">
         <v>182</v>
@@ -59338,7 +59332,7 @@
         <v>-8.778333330000001</v>
       </c>
       <c r="AD104" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE104">
         <v>-0.005556</v>
@@ -59362,7 +59356,7 @@
         <v>-0.363607</v>
       </c>
       <c r="AL104">
-        <v>-27.819186</v>
+        <v>-27.888917</v>
       </c>
       <c r="AM104">
         <v>-0.0017</v>
@@ -59386,7 +59380,7 @@
         <v>-0.363835</v>
       </c>
       <c r="AT104">
-        <v>-8.479288</v>
+        <v>-8.500541999999999</v>
       </c>
     </row>
     <row r="105" spans="1:46">
@@ -59421,7 +59415,7 @@
         <v>786</v>
       </c>
       <c r="K105" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="L105">
         <v>165</v>
@@ -59478,7 +59472,7 @@
         <v>-8.48366667</v>
       </c>
       <c r="AD105" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE105">
         <v>0.032222</v>
@@ -59502,7 +59496,7 @@
         <v>0.023649</v>
       </c>
       <c r="AL105">
-        <v>-27.370651</v>
+        <v>-27.450723</v>
       </c>
       <c r="AM105">
         <v>0.009821999999999999</v>
@@ -59526,7 +59520,7 @@
         <v>0.023665</v>
       </c>
       <c r="AT105">
-        <v>-8.342575</v>
+        <v>-8.366980999999999</v>
       </c>
     </row>
     <row r="106" spans="1:46">
@@ -59561,7 +59555,7 @@
         <v>787</v>
       </c>
       <c r="K106" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="L106">
         <v>199</v>
@@ -59618,7 +59612,7 @@
         <v>-8.42266667</v>
       </c>
       <c r="AD106" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE106">
         <v>0.006667</v>
@@ -59642,7 +59636,7 @@
         <v>-0.23847</v>
       </c>
       <c r="AL106">
-        <v>-27.195366</v>
+        <v>-27.278774</v>
       </c>
       <c r="AM106">
         <v>0.002033</v>
@@ -59666,7 +59660,7 @@
         <v>-0.238461</v>
       </c>
       <c r="AT106">
-        <v>-8.289147</v>
+        <v>-8.314571000000001</v>
       </c>
     </row>
     <row r="107" spans="1:46">
@@ -59701,7 +59695,7 @@
         <v>788</v>
       </c>
       <c r="K107" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="L107">
         <v>174</v>
@@ -59758,7 +59752,7 @@
         <v>-8.23966667</v>
       </c>
       <c r="AD107" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE107">
         <v>0.02</v>
@@ -59782,7 +59776,7 @@
         <v>-0.099971</v>
       </c>
       <c r="AL107">
-        <v>-27.115706</v>
+        <v>-27.200491</v>
       </c>
       <c r="AM107">
         <v>0.0061</v>
@@ -59806,7 +59800,7 @@
         <v>-0.099823</v>
       </c>
       <c r="AT107">
-        <v>-8.264868</v>
+        <v>-8.290711</v>
       </c>
     </row>
     <row r="108" spans="1:46">
@@ -59841,7 +59835,7 @@
         <v>789</v>
       </c>
       <c r="K108" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="L108">
         <v>200</v>
@@ -59898,7 +59892,7 @@
         <v>-8.04666667</v>
       </c>
       <c r="AD108" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE108">
         <v>0.021111</v>
@@ -59922,7 +59916,7 @@
         <v>-0.08799999999999999</v>
       </c>
       <c r="AL108">
-        <v>-26.688325</v>
+        <v>-26.778901</v>
       </c>
       <c r="AM108">
         <v>0.006433</v>
@@ -59946,7 +59940,7 @@
         <v>-0.08805399999999999</v>
       </c>
       <c r="AT108">
-        <v>-8.134601999999999</v>
+        <v>-8.16221</v>
       </c>
     </row>
     <row r="109" spans="1:46">
@@ -59981,7 +59975,7 @@
         <v>790</v>
       </c>
       <c r="K109" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L109">
         <v>181</v>
@@ -60038,7 +60032,7 @@
         <v>-7.95533333</v>
       </c>
       <c r="AD109" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE109">
         <v>0.01</v>
@@ -60062,7 +60056,7 @@
         <v>-0.203131</v>
       </c>
       <c r="AL109">
-        <v>-26.448278</v>
+        <v>-26.540822</v>
       </c>
       <c r="AM109">
         <v>0.003044</v>
@@ -60086,7 +60080,7 @@
         <v>-0.203265</v>
       </c>
       <c r="AT109">
-        <v>-8.061434</v>
+        <v>-8.089642</v>
       </c>
     </row>
     <row r="110" spans="1:46">
@@ -60121,7 +60115,7 @@
         <v>791</v>
       </c>
       <c r="K110" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="L110">
         <v>181</v>
@@ -60178,7 +60172,7 @@
         <v>-7.95533333</v>
       </c>
       <c r="AD110" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE110">
         <v>0</v>
@@ -60202,7 +60196,7 @@
         <v>-0.306563</v>
       </c>
       <c r="AL110">
-        <v>-26.040897</v>
+        <v>-26.134361</v>
       </c>
       <c r="AM110">
         <v>0</v>
@@ -60226,7 +60220,7 @@
         <v>-0.306559</v>
       </c>
       <c r="AT110">
-        <v>-7.937264</v>
+        <v>-7.965752</v>
       </c>
     </row>
     <row r="111" spans="1:46">
@@ -60261,7 +60255,7 @@
         <v>792</v>
       </c>
       <c r="K111" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="L111">
         <v>175</v>
@@ -60318,7 +60312,7 @@
         <v>-7.92483333</v>
       </c>
       <c r="AD111" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE111">
         <v>0.001667</v>
@@ -60342,7 +60336,7 @@
         <v>-0.287566</v>
       </c>
       <c r="AL111">
-        <v>-25.892892</v>
+        <v>-25.985842</v>
       </c>
       <c r="AM111">
         <v>0.000508</v>
@@ -60366,7 +60360,7 @@
         <v>-0.28758</v>
       </c>
       <c r="AT111">
-        <v>-7.89215</v>
+        <v>-7.920481</v>
       </c>
     </row>
     <row r="112" spans="1:46">
@@ -60401,7 +60395,7 @@
         <v>793</v>
       </c>
       <c r="K112" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="L112">
         <v>195</v>
@@ -60458,7 +60452,7 @@
         <v>-7.86366667</v>
       </c>
       <c r="AD112" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE112">
         <v>0.006667</v>
@@ -60482,7 +60476,7 @@
         <v>-0.233508</v>
       </c>
       <c r="AL112">
-        <v>-25.823552</v>
+        <v>-25.916089</v>
       </c>
       <c r="AM112">
         <v>0.002039</v>
@@ -60506,7 +60500,7 @@
         <v>-0.233252</v>
       </c>
       <c r="AT112">
-        <v>-7.87102</v>
+        <v>-7.899226</v>
       </c>
     </row>
     <row r="113" spans="1:46">
@@ -60541,7 +60535,7 @@
         <v>794</v>
       </c>
       <c r="K113" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="L113">
         <v>182</v>
@@ -60598,7 +60592,7 @@
         <v>-7.874</v>
       </c>
       <c r="AD113" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE113">
         <v>-0.001111</v>
@@ -60622,7 +60616,7 @@
         <v>-0.314667</v>
       </c>
       <c r="AL113">
-        <v>-25.449603</v>
+        <v>-25.5378</v>
       </c>
       <c r="AM113">
         <v>-0.000344</v>
@@ -60646,7 +60640,7 @@
         <v>-0.314869</v>
       </c>
       <c r="AT113">
-        <v>-7.757036</v>
+        <v>-7.783919</v>
       </c>
     </row>
     <row r="114" spans="1:46">
@@ -60681,7 +60675,7 @@
         <v>795</v>
       </c>
       <c r="K114" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="L114">
         <v>195</v>
@@ -60738,7 +60732,7 @@
         <v>-7.874</v>
       </c>
       <c r="AD114" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE114">
         <v>0</v>
@@ -60762,7 +60756,7 @@
         <v>-0.30133</v>
       </c>
       <c r="AL114">
-        <v>-25.316636</v>
+        <v>-25.402321</v>
       </c>
       <c r="AM114">
         <v>0</v>
@@ -60786,7 +60780,7 @@
         <v>-0.301354</v>
       </c>
       <c r="AT114">
-        <v>-7.716506</v>
+        <v>-7.742624</v>
       </c>
     </row>
     <row r="115" spans="1:46">
@@ -60821,7 +60815,7 @@
         <v>796</v>
       </c>
       <c r="K115" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="L115">
         <v>195</v>
@@ -60878,7 +60872,7 @@
         <v>-7.90466667</v>
       </c>
       <c r="AD115" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE115">
         <v>-0.003333</v>
@@ -60902,7 +60896,7 @@
         <v>-0.335418</v>
       </c>
       <c r="AL115">
-        <v>-25.252784</v>
+        <v>-25.337057</v>
       </c>
       <c r="AM115">
         <v>-0.001022</v>
@@ -60926,7 +60920,7 @@
         <v>-0.335641</v>
       </c>
       <c r="AT115">
-        <v>-7.697045</v>
+        <v>-7.722732</v>
       </c>
     </row>
     <row r="116" spans="1:46">
@@ -60961,7 +60955,7 @@
         <v>797</v>
       </c>
       <c r="K116" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="L116">
         <v>189</v>
@@ -61018,7 +61012,7 @@
         <v>-7.70133333</v>
       </c>
       <c r="AD116" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE116">
         <v>0.022222</v>
@@ -61042,7 +61036,7 @@
         <v>-0.060045</v>
       </c>
       <c r="AL116">
-        <v>-24.93821</v>
+        <v>-25.013293</v>
       </c>
       <c r="AM116">
         <v>0.006778</v>
@@ -61066,7 +61060,7 @@
         <v>-0.059886</v>
       </c>
       <c r="AT116">
-        <v>-7.601162</v>
+        <v>-7.624048</v>
       </c>
     </row>
     <row r="117" spans="1:46">
@@ -61101,7 +61095,7 @@
         <v>798</v>
       </c>
       <c r="K117" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="L117">
         <v>219</v>
@@ -61158,7 +61152,7 @@
         <v>-7.691</v>
       </c>
       <c r="AD117" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE117">
         <v>0.001111</v>
@@ -61182,7 +61176,7 @@
         <v>-0.286971</v>
       </c>
       <c r="AL117">
-        <v>-24.824623</v>
+        <v>-24.89533</v>
       </c>
       <c r="AM117">
         <v>0.000344</v>
@@ -61206,7 +61200,7 @@
         <v>-0.286778</v>
       </c>
       <c r="AT117">
-        <v>-7.566542</v>
+        <v>-7.588094</v>
       </c>
     </row>
     <row r="118" spans="1:46">
@@ -61241,7 +61235,7 @@
         <v>799</v>
       </c>
       <c r="K118" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="L118">
         <v>186</v>
@@ -61298,7 +61292,7 @@
         <v>-7.67066667</v>
       </c>
       <c r="AD118" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE118">
         <v>0.002222</v>
@@ -61322,7 +61316,7 @@
         <v>-0.273644</v>
       </c>
       <c r="AL118">
-        <v>-24.771466</v>
+        <v>-24.8399</v>
       </c>
       <c r="AM118">
         <v>0.000678</v>
@@ -61346,7 +61340,7 @@
         <v>-0.273631</v>
       </c>
       <c r="AT118">
-        <v>-7.550341</v>
+        <v>-7.571201</v>
       </c>
     </row>
     <row r="119" spans="1:46">
@@ -61381,7 +61375,7 @@
         <v>800</v>
       </c>
       <c r="K119" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="L119">
         <v>212</v>
@@ -61438,7 +61432,7 @@
         <v>-7.72166667</v>
       </c>
       <c r="AD119" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE119">
         <v>-0.005556</v>
@@ -61462,7 +61456,7 @@
         <v>-0.356713</v>
       </c>
       <c r="AL119">
-        <v>-24.506542</v>
+        <v>-24.561104</v>
       </c>
       <c r="AM119">
         <v>-0.0017</v>
@@ -61486,7 +61480,7 @@
         <v>-0.356956</v>
       </c>
       <c r="AT119">
-        <v>-7.469588</v>
+        <v>-7.486219</v>
       </c>
     </row>
     <row r="120" spans="1:46">
@@ -61521,7 +61515,7 @@
         <v>801</v>
       </c>
       <c r="K120" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="L120">
         <v>187</v>
@@ -61578,7 +61572,7 @@
         <v>-7.73166667</v>
       </c>
       <c r="AD120" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE120">
         <v>-0.001111</v>
@@ -61602,7 +61596,7 @@
         <v>-0.306651</v>
       </c>
       <c r="AL120">
-        <v>-24.413904</v>
+        <v>-24.462413</v>
       </c>
       <c r="AM120">
         <v>-0.000333</v>
@@ -61626,7 +61620,7 @@
         <v>-0.306448</v>
       </c>
       <c r="AT120">
-        <v>-7.441356</v>
+        <v>-7.456142</v>
       </c>
     </row>
     <row r="121" spans="1:46">
@@ -61661,7 +61655,7 @@
         <v>802</v>
       </c>
       <c r="K121" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="L121">
         <v>201</v>
@@ -61718,7 +61712,7 @@
         <v>-7.62</v>
       </c>
       <c r="AD121" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE121">
         <v>0.012222</v>
@@ -61742,7 +61736,7 @@
         <v>-0.15951</v>
       </c>
       <c r="AL121">
-        <v>-24.376427</v>
+        <v>-24.422272</v>
       </c>
       <c r="AM121">
         <v>0.003722</v>
@@ -61766,7 +61760,7 @@
         <v>-0.159634</v>
       </c>
       <c r="AT121">
-        <v>-7.429932</v>
+        <v>-7.443907</v>
       </c>
     </row>
     <row r="122" spans="1:46">
@@ -61801,7 +61795,7 @@
         <v>803</v>
       </c>
       <c r="K122" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="L122">
         <v>179</v>
@@ -61858,7 +61852,7 @@
         <v>-7.559</v>
       </c>
       <c r="AD122" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE122">
         <v>0.006667</v>
@@ -61882,7 +61876,7 @@
         <v>-0.219821</v>
       </c>
       <c r="AL122">
-        <v>-24.170835</v>
+        <v>-24.199357</v>
       </c>
       <c r="AM122">
         <v>0.002033</v>
@@ -61906,7 +61900,7 @@
         <v>-0.219788</v>
       </c>
       <c r="AT122">
-        <v>-7.367266</v>
+        <v>-7.37596</v>
       </c>
     </row>
     <row r="123" spans="1:46">
@@ -61941,7 +61935,7 @@
         <v>804</v>
       </c>
       <c r="K123" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="L123">
         <v>207</v>
@@ -61998,7 +61992,7 @@
         <v>-7.58966667</v>
       </c>
       <c r="AD123" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE123">
         <v>-0.003333</v>
@@ -62022,7 +62016,7 @@
         <v>-0.329061</v>
       </c>
       <c r="AL123">
-        <v>-24.099191</v>
+        <v>-24.120328</v>
       </c>
       <c r="AM123">
         <v>-0.001022</v>
@@ -62046,7 +62040,7 @@
         <v>-0.329297</v>
       </c>
       <c r="AT123">
-        <v>-7.345429</v>
+        <v>-7.351872</v>
       </c>
     </row>
     <row r="124" spans="1:46">
@@ -62081,7 +62075,7 @@
         <v>805</v>
       </c>
       <c r="K124" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="L124">
         <v>209</v>
@@ -62138,7 +62132,7 @@
         <v>-7.57933333</v>
       </c>
       <c r="AD124" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE124">
         <v>0.001111</v>
@@ -62162,7 +62156,7 @@
         <v>-0.278432</v>
       </c>
       <c r="AL124">
-        <v>-24.071422</v>
+        <v>-24.089459</v>
       </c>
       <c r="AM124">
         <v>0.000344</v>
@@ -62186,7 +62180,7 @@
         <v>-0.278235</v>
       </c>
       <c r="AT124">
-        <v>-7.336967</v>
+        <v>-7.342465</v>
       </c>
     </row>
     <row r="125" spans="1:46">
@@ -62221,7 +62215,7 @@
         <v>806</v>
       </c>
       <c r="K125" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L125">
         <v>179</v>
@@ -62278,7 +62272,7 @@
         <v>-7.53866667</v>
       </c>
       <c r="AD125" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE125">
         <v>0.004444</v>
@@ -62302,7 +62296,7 @@
         <v>-0.240207</v>
       </c>
       <c r="AL125">
-        <v>-23.922786</v>
+        <v>-23.921311</v>
       </c>
       <c r="AM125">
         <v>0.001356</v>
@@ -62326,7 +62320,7 @@
         <v>-0.240141</v>
       </c>
       <c r="AT125">
-        <v>-7.291661</v>
+        <v>-7.291212</v>
       </c>
     </row>
     <row r="126" spans="1:46">
@@ -62361,7 +62355,7 @@
         <v>807</v>
       </c>
       <c r="K126" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="L126">
         <v>181</v>
@@ -62418,7 +62412,7 @@
         <v>-7.47766667</v>
       </c>
       <c r="AD126" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE126">
         <v>0.006667</v>
@@ -62442,7 +62436,7 @@
         <v>-0.214401</v>
       </c>
       <c r="AL126">
-        <v>-23.874093</v>
+        <v>-23.864825</v>
       </c>
       <c r="AM126">
         <v>0.002033</v>
@@ -62466,7 +62460,7 @@
         <v>-0.214367</v>
       </c>
       <c r="AT126">
-        <v>-7.276821</v>
+        <v>-7.273996</v>
       </c>
     </row>
     <row r="127" spans="1:46">
@@ -62501,7 +62495,7 @@
         <v>808</v>
       </c>
       <c r="K127" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="L127">
         <v>198</v>
@@ -62558,7 +62552,7 @@
         <v>-7.478</v>
       </c>
       <c r="AD127" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE127">
         <v>0</v>
@@ -62582,7 +62576,7 @@
         <v>-0.288127</v>
       </c>
       <c r="AL127">
-        <v>-23.854907</v>
+        <v>-23.842316</v>
       </c>
       <c r="AM127">
         <v>-1.1E-05</v>
@@ -62606,7 +62600,7 @@
         <v>-0.288523</v>
       </c>
       <c r="AT127">
-        <v>-7.270971</v>
+        <v>-7.267133</v>
       </c>
     </row>
     <row r="128" spans="1:46">
@@ -62641,7 +62635,7 @@
         <v>809</v>
       </c>
       <c r="K128" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="L128">
         <v>177</v>
@@ -62698,7 +62692,7 @@
         <v>-7.51833333</v>
       </c>
       <c r="AD128" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE128">
         <v>-0.004444</v>
@@ -62722,7 +62716,7 @@
         <v>-0.336811</v>
       </c>
       <c r="AL128">
-        <v>-23.755153</v>
+        <v>-23.72216</v>
       </c>
       <c r="AM128">
         <v>-0.001344</v>
@@ -62746,7 +62740,7 @@
         <v>-0.336418</v>
       </c>
       <c r="AT128">
-        <v>-7.240568</v>
+        <v>-7.230511</v>
       </c>
     </row>
     <row r="129" spans="1:46">
@@ -62781,7 +62775,7 @@
         <v>810</v>
       </c>
       <c r="K129" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L129">
         <v>186</v>
@@ -62838,7 +62832,7 @@
         <v>-7.45766667</v>
       </c>
       <c r="AD129" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE129">
         <v>0.006667</v>
@@ -62862,7 +62856,7 @@
         <v>-0.210079</v>
       </c>
       <c r="AL129">
-        <v>-23.725265</v>
+        <v>-23.684764</v>
       </c>
       <c r="AM129">
         <v>0.002022</v>
@@ -62886,7 +62880,7 @@
         <v>-0.210446</v>
       </c>
       <c r="AT129">
-        <v>-7.231457</v>
+        <v>-7.219112</v>
       </c>
     </row>
     <row r="130" spans="1:46">
@@ -62921,7 +62915,7 @@
         <v>811</v>
       </c>
       <c r="K130" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="L130">
         <v>212</v>
@@ -62978,7 +62972,7 @@
         <v>-7.427</v>
       </c>
       <c r="AD130" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE130">
         <v>0.003333</v>
@@ -63002,7 +62996,7 @@
         <v>-0.246973</v>
       </c>
       <c r="AL130">
-        <v>-23.713747</v>
+        <v>-23.670115</v>
       </c>
       <c r="AM130">
         <v>0.001022</v>
@@ -63026,7 +63020,7 @@
         <v>-0.246733</v>
       </c>
       <c r="AT130">
-        <v>-7.227947</v>
+        <v>-7.214647</v>
       </c>
     </row>
     <row r="131" spans="1:46">
@@ -63061,7 +63055,7 @@
         <v>812</v>
       </c>
       <c r="K131" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="L131">
         <v>175</v>
@@ -63118,7 +63112,7 @@
         <v>-7.22366667</v>
       </c>
       <c r="AD131" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE131">
         <v>0.022222</v>
@@ -63142,7 +63136,7 @@
         <v>-0.031258</v>
       </c>
       <c r="AL131">
-        <v>-23.655716</v>
+        <v>-23.593599</v>
       </c>
       <c r="AM131">
         <v>0.006778</v>
@@ -63166,7 +63160,7 @@
         <v>-0.031089</v>
       </c>
       <c r="AT131">
-        <v>-7.21026</v>
+        <v>-7.191327</v>
       </c>
     </row>
     <row r="132" spans="1:46">
@@ -63201,7 +63195,7 @@
         <v>813</v>
       </c>
       <c r="K132" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="L132">
         <v>184</v>
@@ -63258,7 +63252,7 @@
         <v>-7.16266667</v>
       </c>
       <c r="AD132" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE132">
         <v>0.006667</v>
@@ -63282,7 +63276,7 @@
         <v>-0.20866</v>
       </c>
       <c r="AL132">
-        <v>-23.638645</v>
+        <v>-23.56997</v>
       </c>
       <c r="AM132">
         <v>0.002033</v>
@@ -63306,7 +63300,7 @@
         <v>-0.208626</v>
       </c>
       <c r="AT132">
-        <v>-7.205057</v>
+        <v>-7.184124</v>
       </c>
     </row>
     <row r="133" spans="1:46">
@@ -63341,7 +63335,7 @@
         <v>814</v>
       </c>
       <c r="K133" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="L133">
         <v>223</v>
@@ -63398,7 +63392,7 @@
         <v>-7.22366667</v>
       </c>
       <c r="AD133" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE133">
         <v>-0.006667</v>
@@ -63422,7 +63416,7 @@
         <v>-0.360447</v>
       </c>
       <c r="AL133">
-        <v>-23.631347</v>
+        <v>-23.559675</v>
       </c>
       <c r="AM133">
         <v>-0.002033</v>
@@ -63446,7 +63440,7 @@
         <v>-0.360504</v>
       </c>
       <c r="AT133">
-        <v>-7.202833</v>
+        <v>-7.180986</v>
       </c>
     </row>
     <row r="134" spans="1:46">
@@ -63481,7 +63475,7 @@
         <v>815</v>
       </c>
       <c r="K134" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="L134">
         <v>185</v>
@@ -63538,7 +63532,7 @@
         <v>-7.285</v>
       </c>
       <c r="AD134" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE134">
         <v>-0.006667</v>
@@ -63562,7 +63556,7 @@
         <v>-0.358921</v>
       </c>
       <c r="AL134">
-        <v>-23.596599</v>
+        <v>-23.50914</v>
       </c>
       <c r="AM134">
         <v>-0.002044</v>
@@ -63586,7 +63580,7 @@
         <v>-0.359392</v>
       </c>
       <c r="AT134">
-        <v>-7.192242</v>
+        <v>-7.165584</v>
       </c>
     </row>
     <row r="135" spans="1:46">
@@ -63621,7 +63615,7 @@
         <v>816</v>
       </c>
       <c r="K135" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="L135">
         <v>231</v>
@@ -63678,7 +63672,7 @@
         <v>-7.35566667</v>
       </c>
       <c r="AD135" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE135">
         <v>-0.007778</v>
@@ -63702,7 +63696,7 @@
         <v>-0.370195</v>
       </c>
       <c r="AL135">
-        <v>-23.58539</v>
+        <v>-23.492578</v>
       </c>
       <c r="AM135">
         <v>-0.002356</v>
@@ -63726,7 +63720,7 @@
         <v>-0.369641</v>
       </c>
       <c r="AT135">
-        <v>-7.188826</v>
+        <v>-7.160537</v>
       </c>
     </row>
     <row r="136" spans="1:46">
@@ -63761,7 +63755,7 @@
         <v>817</v>
       </c>
       <c r="K136" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L136">
         <v>169</v>
@@ -63818,7 +63812,7 @@
         <v>-7.35566667</v>
       </c>
       <c r="AD136" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE136">
         <v>0</v>
@@ -63842,7 +63836,7 @@
         <v>-0.278734</v>
       </c>
       <c r="AL136">
-        <v>-23.580524</v>
+        <v>-23.485445</v>
       </c>
       <c r="AM136">
         <v>0</v>
@@ -63866,7 +63860,7 @@
         <v>-0.278721</v>
       </c>
       <c r="AT136">
-        <v>-7.187343</v>
+        <v>-7.158363</v>
       </c>
     </row>
     <row r="137" spans="1:46">
@@ -63901,7 +63895,7 @@
         <v>818</v>
       </c>
       <c r="K137" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="L137">
         <v>230</v>
@@ -63958,7 +63952,7 @@
         <v>-7.22366667</v>
       </c>
       <c r="AD137" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE137">
         <v>0.014444</v>
@@ -63982,7 +63976,7 @@
         <v>-0.109942</v>
       </c>
       <c r="AL137">
-        <v>-23.553482</v>
+        <v>-23.447753</v>
       </c>
       <c r="AM137">
         <v>0.0044</v>
@@ -64006,7 +64000,7 @@
         <v>-0.110053</v>
       </c>
       <c r="AT137">
-        <v>-7.179101</v>
+        <v>-7.146874</v>
       </c>
     </row>
     <row r="138" spans="1:46">
@@ -64041,7 +64035,7 @@
         <v>819</v>
       </c>
       <c r="K138" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="L138">
         <v>146</v>
@@ -64098,7 +64092,7 @@
         <v>-7.19333333</v>
       </c>
       <c r="AD138" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE138">
         <v>0.003333</v>
@@ -64122,7 +64116,7 @@
         <v>-0.239019</v>
       </c>
       <c r="AL138">
-        <v>-23.541862</v>
+        <v>-23.43298</v>
       </c>
       <c r="AM138">
         <v>0.001011</v>
@@ -64146,7 +64140,7 @@
         <v>-0.239214</v>
       </c>
       <c r="AT138">
-        <v>-7.17556</v>
+        <v>-7.142372</v>
       </c>
     </row>
     <row r="139" spans="1:46">
@@ -64181,7 +64175,7 @@
         <v>820</v>
       </c>
       <c r="K139" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L139">
         <v>194</v>
@@ -64238,7 +64232,7 @@
         <v>-7.01066667</v>
       </c>
       <c r="AD139" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE139">
         <v>0.02</v>
@@ -64262,7 +64256,7 @@
         <v>-0.043177</v>
       </c>
       <c r="AL139">
-        <v>-23.53741</v>
+        <v>-23.427547</v>
       </c>
       <c r="AM139">
         <v>0.006089</v>
@@ -64286,7 +64280,7 @@
         <v>-0.043456</v>
       </c>
       <c r="AT139">
-        <v>-7.174203</v>
+        <v>-7.140716</v>
       </c>
     </row>
     <row r="140" spans="1:46">
@@ -64321,7 +64315,7 @@
         <v>821</v>
       </c>
       <c r="K140" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L140">
         <v>167</v>
@@ -64378,7 +64372,7 @@
         <v>-6.90866667</v>
       </c>
       <c r="AD140" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE140">
         <v>0.011111</v>
@@ -64402,7 +64396,7 @@
         <v>-0.147382</v>
       </c>
       <c r="AL140">
-        <v>-23.499725</v>
+        <v>-23.385352</v>
       </c>
       <c r="AM140">
         <v>0.0034</v>
@@ -64426,7 +64420,7 @@
         <v>-0.146865</v>
       </c>
       <c r="AT140">
-        <v>-7.162718</v>
+        <v>-7.127856</v>
       </c>
     </row>
     <row r="141" spans="1:46">
@@ -64461,7 +64455,7 @@
         <v>822</v>
       </c>
       <c r="K141" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L141">
         <v>167</v>
@@ -64518,7 +64512,7 @@
         <v>-6.83766667</v>
       </c>
       <c r="AD141" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE141">
         <v>0.007778</v>
@@ -64542,7 +64536,7 @@
         <v>-0.186103</v>
       </c>
       <c r="AL141">
-        <v>-23.481254</v>
+        <v>-23.366308</v>
       </c>
       <c r="AM141">
         <v>0.002367</v>
@@ -64566,7 +64560,7 @@
         <v>-0.186239</v>
       </c>
       <c r="AT141">
-        <v>-7.157088</v>
+        <v>-7.122052</v>
       </c>
     </row>
     <row r="142" spans="1:46">
@@ -64601,7 +64595,7 @@
         <v>823</v>
       </c>
       <c r="K142" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="L142">
         <v>204</v>
@@ -64658,7 +64652,7 @@
         <v>-6.90866667</v>
       </c>
       <c r="AD142" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE142">
         <v>-0.007778</v>
@@ -64682,7 +64676,7 @@
         <v>-0.369223</v>
       </c>
       <c r="AL142">
-        <v>-23.472784</v>
+        <v>-23.357799</v>
       </c>
       <c r="AM142">
         <v>-0.002367</v>
@@ -64706,7 +64700,7 @@
         <v>-0.369073</v>
       </c>
       <c r="AT142">
-        <v>-7.154507</v>
+        <v>-7.119458</v>
       </c>
     </row>
     <row r="143" spans="1:46">
@@ -64741,7 +64735,7 @@
         <v>824</v>
       </c>
       <c r="K143" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="L143">
         <v>132</v>
@@ -64798,7 +64792,7 @@
         <v>-6.87833333</v>
       </c>
       <c r="AD143" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE143">
         <v>0.003333</v>
@@ -64822,7 +64816,7 @@
         <v>-0.236066</v>
       </c>
       <c r="AL143">
-        <v>-23.406774</v>
+        <v>-23.294265</v>
       </c>
       <c r="AM143">
         <v>0.001011</v>
@@ -64846,7 +64840,7 @@
         <v>-0.236244</v>
       </c>
       <c r="AT143">
-        <v>-7.134388</v>
+        <v>-7.100095</v>
       </c>
     </row>
     <row r="144" spans="1:46">
@@ -64881,7 +64875,7 @@
         <v>825</v>
       </c>
       <c r="K144" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="L144">
         <v>202</v>
@@ -64938,7 +64932,7 @@
         <v>-6.919</v>
       </c>
       <c r="AD144" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE144">
         <v>-0.004444</v>
@@ -64962,7 +64956,7 @@
         <v>-0.327689</v>
       </c>
       <c r="AL144">
-        <v>-23.373526</v>
+        <v>-23.263332</v>
       </c>
       <c r="AM144">
         <v>-0.001356</v>
@@ -64986,7 +64980,7 @@
         <v>-0.327737</v>
       </c>
       <c r="AT144">
-        <v>-7.124255</v>
+        <v>-7.090666</v>
       </c>
     </row>
     <row r="145" spans="1:46">
@@ -65021,7 +65015,7 @@
         <v>826</v>
       </c>
       <c r="K145" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L145">
         <v>163</v>
@@ -65078,7 +65072,7 @@
         <v>-7.02066667</v>
       </c>
       <c r="AD145" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE145">
         <v>-0.011111</v>
@@ -65102,7 +65096,7 @@
         <v>-0.405923</v>
       </c>
       <c r="AL145">
-        <v>-23.356592</v>
+        <v>-23.247729</v>
       </c>
       <c r="AM145">
         <v>-0.003389</v>
@@ -65126,7 +65120,7 @@
         <v>-0.406033</v>
       </c>
       <c r="AT145">
-        <v>-7.119092</v>
+        <v>-7.08591</v>
       </c>
     </row>
     <row r="146" spans="1:46">
@@ -65161,7 +65155,7 @@
         <v>827</v>
       </c>
       <c r="K146" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="L146">
         <v>205</v>
@@ -65218,7 +65212,7 @@
         <v>-7.041</v>
       </c>
       <c r="AD146" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE146">
         <v>-0.002222</v>
@@ -65242,7 +65236,7 @@
         <v>-0.297961</v>
       </c>
       <c r="AL146">
-        <v>-23.243873</v>
+        <v>-23.145316</v>
       </c>
       <c r="AM146">
         <v>-0.000678</v>
@@ -65266,7 +65260,7 @@
         <v>-0.297994</v>
       </c>
       <c r="AT146">
-        <v>-7.084736</v>
+        <v>-7.054696</v>
       </c>
     </row>
     <row r="147" spans="1:46">
@@ -65301,7 +65295,7 @@
         <v>828</v>
       </c>
       <c r="K147" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="L147">
         <v>98</v>
@@ -65358,7 +65352,7 @@
         <v>-7.00033333</v>
       </c>
       <c r="AD147" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE147">
         <v>0.004444</v>
@@ -65382,7 +65376,7 @@
         <v>-0.216811</v>
       </c>
       <c r="AL147">
-        <v>-23.190961</v>
+        <v>-23.097707</v>
       </c>
       <c r="AM147">
         <v>0.001356</v>
@@ -65406,7 +65400,7 @@
         <v>-0.216749</v>
       </c>
       <c r="AT147">
-        <v>-7.06861</v>
+        <v>-7.040185</v>
       </c>
     </row>
     <row r="148" spans="1:46">
@@ -65441,7 +65435,7 @@
         <v>829</v>
       </c>
       <c r="K148" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="L148">
         <v>157</v>
@@ -65498,7 +65492,7 @@
         <v>-6.939</v>
       </c>
       <c r="AD148" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE148">
         <v>0.006667</v>
@@ -65522,7 +65516,7 @@
         <v>-0.189241</v>
       </c>
       <c r="AL148">
-        <v>-23.165984</v>
+        <v>-23.075284</v>
       </c>
       <c r="AM148">
         <v>0.002044</v>
@@ -65546,7 +65540,7 @@
         <v>-0.188762</v>
       </c>
       <c r="AT148">
-        <v>-7.060999</v>
+        <v>-7.033352</v>
       </c>
     </row>
     <row r="149" spans="1:46">
@@ -65581,7 +65575,7 @@
         <v>830</v>
       </c>
       <c r="K149" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="L149">
         <v>141</v>
@@ -65638,7 +65632,7 @@
         <v>-6.98</v>
       </c>
       <c r="AD149" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE149">
         <v>-0.004444</v>
@@ -65662,7 +65656,7 @@
         <v>-0.322899</v>
       </c>
       <c r="AL149">
-        <v>-22.991614</v>
+        <v>-22.919141</v>
       </c>
       <c r="AM149">
         <v>-0.001367</v>
@@ -65686,7 +65680,7 @@
         <v>-0.3234</v>
       </c>
       <c r="AT149">
-        <v>-7.007848</v>
+        <v>-6.985758</v>
       </c>
     </row>
     <row r="150" spans="1:46">
@@ -65721,7 +65715,7 @@
         <v>831</v>
       </c>
       <c r="K150" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="L150">
         <v>144</v>
@@ -65778,7 +65772,7 @@
         <v>-6.96966667</v>
       </c>
       <c r="AD150" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE150">
         <v>0.001111</v>
@@ -65802,7 +65796,7 @@
         <v>-0.254348</v>
       </c>
       <c r="AL150">
-        <v>-22.914167</v>
+        <v>-22.849841</v>
       </c>
       <c r="AM150">
         <v>0.000344</v>
@@ -65826,7 +65820,7 @@
         <v>-0.254148</v>
       </c>
       <c r="AT150">
-        <v>-6.984245</v>
+        <v>-6.964638</v>
       </c>
     </row>
     <row r="151" spans="1:46">
@@ -65861,7 +65855,7 @@
         <v>832</v>
       </c>
       <c r="K151" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="L151">
         <v>194</v>
@@ -65918,7 +65912,7 @@
         <v>-6.80733333</v>
       </c>
       <c r="AD151" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE151">
         <v>0.017778</v>
@@ -65942,7 +65936,7 @@
         <v>-0.050603</v>
       </c>
       <c r="AL151">
-        <v>-22.885916</v>
+        <v>-22.824554</v>
       </c>
       <c r="AM151">
         <v>0.005411</v>
@@ -65966,7 +65960,7 @@
         <v>-0.050905</v>
       </c>
       <c r="AT151">
-        <v>-6.975634</v>
+        <v>-6.95693</v>
       </c>
     </row>
     <row r="152" spans="1:46">
@@ -66001,7 +65995,7 @@
         <v>833</v>
       </c>
       <c r="K152" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="L152">
         <v>140</v>
@@ -66058,7 +66052,7 @@
         <v>-6.56333333</v>
       </c>
       <c r="AD152" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE152">
         <v>0.026667</v>
@@ -66082,7 +66076,7 @@
         <v>0.058139</v>
       </c>
       <c r="AL152">
-        <v>-22.657716</v>
+        <v>-22.619982</v>
       </c>
       <c r="AM152">
         <v>0.008133</v>
@@ -66106,7 +66100,7 @@
         <v>0.058337</v>
       </c>
       <c r="AT152">
-        <v>-6.906077</v>
+        <v>-6.894575</v>
       </c>
     </row>
     <row r="153" spans="1:46">
@@ -66141,7 +66135,7 @@
         <v>834</v>
       </c>
       <c r="K153" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="L153">
         <v>157</v>
@@ -66198,7 +66192,7 @@
         <v>-6.45166667</v>
       </c>
       <c r="AD153" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE153">
         <v>0.012222</v>
@@ -66222,7 +66216,7 @@
         <v>-0.11908</v>
       </c>
       <c r="AL153">
-        <v>-22.561663</v>
+        <v>-22.533656</v>
       </c>
       <c r="AM153">
         <v>0.003722</v>
@@ -66246,7 +66240,7 @@
         <v>-0.119207</v>
       </c>
       <c r="AT153">
-        <v>-6.876802</v>
+        <v>-6.868265</v>
       </c>
     </row>
     <row r="154" spans="1:46">
@@ -66281,7 +66275,7 @@
         <v>835</v>
       </c>
       <c r="K154" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="L154">
         <v>182</v>
@@ -66338,7 +66332,7 @@
         <v>-6.45166667</v>
       </c>
       <c r="AD154" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE154">
         <v>0</v>
@@ -66362,7 +66356,7 @@
         <v>-0.268916</v>
       </c>
       <c r="AL154">
-        <v>-22.5247</v>
+        <v>-22.500396</v>
       </c>
       <c r="AM154">
         <v>0</v>
@@ -66386,7 +66380,7 @@
         <v>-0.268911</v>
       </c>
       <c r="AT154">
-        <v>-6.865535</v>
+        <v>-6.858127</v>
       </c>
     </row>
     <row r="155" spans="1:46">
@@ -66421,7 +66415,7 @@
         <v>836</v>
       </c>
       <c r="K155" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="L155">
         <v>145</v>
@@ -66478,7 +66472,7 @@
         <v>-6.36</v>
       </c>
       <c r="AD155" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE155">
         <v>0.01</v>
@@ -66502,7 +66496,7 @@
         <v>-0.144689</v>
       </c>
       <c r="AL155">
-        <v>-22.240306</v>
+        <v>-22.243704</v>
       </c>
       <c r="AM155">
         <v>0.003056</v>
@@ -66526,7 +66520,7 @@
         <v>-0.144358</v>
       </c>
       <c r="AT155">
-        <v>-6.778854</v>
+        <v>-6.779889</v>
       </c>
     </row>
     <row r="156" spans="1:46">
@@ -66561,7 +66555,7 @@
         <v>837</v>
       </c>
       <c r="K156" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L156">
         <v>169</v>
@@ -66618,7 +66612,7 @@
         <v>-6.36033333</v>
       </c>
       <c r="AD156" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE156">
         <v>0</v>
@@ -66642,7 +66636,7 @@
         <v>-0.267908</v>
       </c>
       <c r="AL156">
-        <v>-22.121576</v>
+        <v>-22.136107</v>
       </c>
       <c r="AM156">
         <v>-1.1E-05</v>
@@ -66666,7 +66660,7 @@
         <v>-0.268355</v>
       </c>
       <c r="AT156">
-        <v>-6.74266</v>
+        <v>-6.747089</v>
       </c>
     </row>
     <row r="157" spans="1:46">
@@ -66701,7 +66695,7 @@
         <v>838</v>
       </c>
       <c r="K157" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="L157">
         <v>162</v>
@@ -66758,7 +66752,7 @@
         <v>-6.289</v>
       </c>
       <c r="AD157" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE157">
         <v>0.007778</v>
@@ -66782,7 +66776,7 @@
         <v>-0.170487</v>
       </c>
       <c r="AL157">
-        <v>-21.74243</v>
+        <v>-21.790731</v>
       </c>
       <c r="AM157">
         <v>0.002378</v>
@@ -66806,7 +66800,7 @@
         <v>-0.170178</v>
       </c>
       <c r="AT157">
-        <v>-6.627102</v>
+        <v>-6.641825</v>
       </c>
     </row>
     <row r="158" spans="1:46">
@@ -66841,7 +66835,7 @@
         <v>839</v>
       </c>
       <c r="K158" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="L158">
         <v>178</v>
@@ -66898,7 +66892,7 @@
         <v>-6.25833333</v>
       </c>
       <c r="AD158" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE158">
         <v>0.003333</v>
@@ -66922,7 +66916,7 @@
         <v>-0.22526</v>
       </c>
       <c r="AL158">
-        <v>-21.607111</v>
+        <v>-21.666789</v>
       </c>
       <c r="AM158">
         <v>0.001022</v>
@@ -66946,7 +66940,7 @@
         <v>-0.225013</v>
       </c>
       <c r="AT158">
-        <v>-6.585857</v>
+        <v>-6.604046</v>
       </c>
     </row>
     <row r="159" spans="1:46">
@@ -66981,7 +66975,7 @@
         <v>840</v>
       </c>
       <c r="K159" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="L159">
         <v>199</v>
@@ -67038,7 +67032,7 @@
         <v>-6.411</v>
       </c>
       <c r="AD159" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE159">
         <v>-0.016667</v>
@@ -67062,7 +67056,7 @@
         <v>-0.474027</v>
       </c>
       <c r="AL159">
-        <v>-21.16525</v>
+        <v>-21.259454</v>
       </c>
       <c r="AM159">
         <v>-0.005089</v>
@@ -67086,7 +67080,7 @@
         <v>-0.474385</v>
       </c>
       <c r="AT159">
-        <v>-6.451177</v>
+        <v>-6.479891</v>
       </c>
     </row>
     <row r="160" spans="1:46">
@@ -67121,7 +67115,7 @@
         <v>841</v>
       </c>
       <c r="K160" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="L160">
         <v>156</v>
@@ -67178,7 +67172,7 @@
         <v>-6.401</v>
       </c>
       <c r="AD160" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE160">
         <v>0.001111</v>
@@ -67202,7 +67196,7 @@
         <v>-0.249846</v>
       </c>
       <c r="AL160">
-        <v>-21.017872</v>
+        <v>-21.122648</v>
       </c>
       <c r="AM160">
         <v>0.000333</v>
@@ -67226,7 +67220,7 @@
         <v>-0.250103</v>
       </c>
       <c r="AT160">
-        <v>-6.40625</v>
+        <v>-6.438187</v>
       </c>
     </row>
     <row r="161" spans="1:46">
@@ -67261,7 +67255,7 @@
         <v>842</v>
       </c>
       <c r="K161" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="L161">
         <v>155</v>
@@ -67318,7 +67312,7 @@
         <v>-6.31611111</v>
       </c>
       <c r="AD161" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE161">
         <v>0.003086</v>
@@ -67342,7 +67336,7 @@
         <v>-0.224225</v>
       </c>
       <c r="AL161">
-        <v>-20.968311</v>
+        <v>-21.076529</v>
       </c>
       <c r="AM161">
         <v>0.000943</v>
@@ -67366,7 +67360,7 @@
         <v>-0.224116</v>
       </c>
       <c r="AT161">
-        <v>-6.391149</v>
+        <v>-6.424134</v>
       </c>
     </row>
     <row r="162" spans="1:46">
@@ -67401,7 +67395,7 @@
         <v>843</v>
       </c>
       <c r="K162" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="L162">
         <v>197</v>
@@ -67458,7 +67452,7 @@
         <v>-6.228</v>
       </c>
       <c r="AD162" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE162">
         <v>0.00963</v>
@@ -67482,7 +67476,7 @@
         <v>-0.141071</v>
       </c>
       <c r="AL162">
-        <v>-20.566251</v>
+        <v>-20.700127</v>
       </c>
       <c r="AM162">
         <v>0.002937</v>
@@ -67506,7 +67500,7 @@
         <v>-0.140997</v>
       </c>
       <c r="AT162">
-        <v>-6.268603</v>
+        <v>-6.309409</v>
       </c>
     </row>
     <row r="163" spans="1:46">
@@ -67541,7 +67535,7 @@
         <v>844</v>
       </c>
       <c r="K163" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="L163">
         <v>137</v>
@@ -67598,7 +67592,7 @@
         <v>-6.18733333</v>
       </c>
       <c r="AD163" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE163">
         <v>0.004444</v>
@@ -67622,7 +67616,7 @@
         <v>-0.206154</v>
       </c>
       <c r="AL163">
-        <v>-20.419323</v>
+        <v>-20.561474</v>
       </c>
       <c r="AM163">
         <v>0.001356</v>
@@ -67646,7 +67640,7 @@
         <v>-0.206082</v>
       </c>
       <c r="AT163">
-        <v>-6.223815</v>
+        <v>-6.267143</v>
       </c>
     </row>
     <row r="164" spans="1:46">
@@ -67681,7 +67675,7 @@
         <v>845</v>
       </c>
       <c r="K164" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="L164">
         <v>197</v>
@@ -67738,7 +67732,7 @@
         <v>-6.218</v>
       </c>
       <c r="AD164" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE164">
         <v>-0.003333</v>
@@ -67762,7 +67756,7 @@
         <v>-0.304018</v>
       </c>
       <c r="AL164">
-        <v>-20.366238</v>
+        <v>-20.511217</v>
       </c>
       <c r="AM164">
         <v>-0.001022</v>
@@ -67786,7 +67780,7 @@
         <v>-0.304271</v>
       </c>
       <c r="AT164">
-        <v>-6.207633</v>
+        <v>-6.251824</v>
       </c>
     </row>
     <row r="165" spans="1:46">
@@ -67821,7 +67815,7 @@
         <v>846</v>
       </c>
       <c r="K165" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="L165">
         <v>167</v>
@@ -67878,7 +67872,7 @@
         <v>-6.22833333</v>
       </c>
       <c r="AD165" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE165">
         <v>-0.001111</v>
@@ -67902,7 +67896,7 @@
         <v>-0.274773</v>
       </c>
       <c r="AL165">
-        <v>-19.970297</v>
+        <v>-20.13328</v>
       </c>
       <c r="AM165">
         <v>-0.000344</v>
@@ -67926,7 +67920,7 @@
         <v>-0.275016</v>
       </c>
       <c r="AT165">
-        <v>-6.086948</v>
+        <v>-6.136626</v>
       </c>
     </row>
     <row r="166" spans="1:46">
@@ -67961,7 +67955,7 @@
         <v>847</v>
       </c>
       <c r="K166" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="L166">
         <v>182</v>
@@ -68018,7 +68012,7 @@
         <v>-6.19766667</v>
       </c>
       <c r="AD166" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE166">
         <v>0.003333</v>
@@ -68042,7 +68036,7 @@
         <v>-0.21725</v>
       </c>
       <c r="AL166">
-        <v>-19.834261</v>
+        <v>-20.001957</v>
       </c>
       <c r="AM166">
         <v>0.001022</v>
@@ -68066,7 +68060,7 @@
         <v>-0.217</v>
       </c>
       <c r="AT166">
-        <v>-6.045484</v>
+        <v>-6.096599</v>
       </c>
     </row>
     <row r="167" spans="1:46">
@@ -68101,7 +68095,7 @@
         <v>848</v>
       </c>
       <c r="K167" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="L167">
         <v>226</v>
@@ -68158,7 +68152,7 @@
         <v>-6.19766667</v>
       </c>
       <c r="AD167" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE167">
         <v>0</v>
@@ -68182,7 +68176,7 @@
         <v>-0.259158</v>
       </c>
       <c r="AL167">
-        <v>-19.784873</v>
+        <v>-19.954058</v>
       </c>
       <c r="AM167">
         <v>0</v>
@@ -68206,7 +68200,7 @@
         <v>-0.259147</v>
       </c>
       <c r="AT167">
-        <v>-6.03043</v>
+        <v>-6.081999</v>
       </c>
     </row>
     <row r="168" spans="1:46">
@@ -68241,7 +68235,7 @@
         <v>849</v>
       </c>
       <c r="K168" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="L168">
         <v>179</v>
@@ -68298,7 +68292,7 @@
         <v>-6.20766667</v>
       </c>
       <c r="AD168" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE168">
         <v>-0.001111</v>
@@ -68322,7 +68316,7 @@
         <v>-0.272565</v>
       </c>
       <c r="AL168">
-        <v>-19.430399</v>
+        <v>-19.605909</v>
       </c>
       <c r="AM168">
         <v>-0.000333</v>
@@ -68346,7 +68340,7 @@
         <v>-0.272312</v>
       </c>
       <c r="AT168">
-        <v>-5.922387</v>
+        <v>-5.975884</v>
       </c>
     </row>
     <row r="169" spans="1:46">
@@ -68381,7 +68375,7 @@
         <v>850</v>
       </c>
       <c r="K169" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="L169">
         <v>205</v>
@@ -68438,7 +68432,7 @@
         <v>-6.21766667</v>
       </c>
       <c r="AD169" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE169">
         <v>-0.001111</v>
@@ -68462,7 +68456,7 @@
         <v>-0.271701</v>
       </c>
       <c r="AL169">
-        <v>-19.31503</v>
+        <v>-19.490448</v>
       </c>
       <c r="AM169">
         <v>-0.000333</v>
@@ -68486,7 +68480,7 @@
         <v>-0.271462</v>
       </c>
       <c r="AT169">
-        <v>-5.887227</v>
+        <v>-5.940695</v>
       </c>
     </row>
     <row r="170" spans="1:46">
@@ -68521,7 +68515,7 @@
         <v>851</v>
       </c>
       <c r="K170" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="L170">
         <v>223</v>
@@ -68578,7 +68572,7 @@
         <v>-6.11633333</v>
       </c>
       <c r="AD170" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE170">
         <v>0.011111</v>
@@ -68602,7 +68596,7 @@
         <v>-0.113266</v>
       </c>
       <c r="AL170">
-        <v>-19.281896</v>
+        <v>-19.457025</v>
       </c>
       <c r="AM170">
         <v>0.003378</v>
@@ -68626,7 +68620,7 @@
         <v>-0.113641</v>
       </c>
       <c r="AT170">
-        <v>-5.87712</v>
+        <v>-5.930501</v>
       </c>
     </row>
     <row r="171" spans="1:46">
@@ -68661,7 +68655,7 @@
         <v>852</v>
       </c>
       <c r="K171" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="L171">
         <v>220</v>
@@ -68718,7 +68712,7 @@
         <v>-6.08566667</v>
       </c>
       <c r="AD171" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE171">
         <v>0.003333</v>
@@ -68742,7 +68736,7 @@
         <v>-0.213517</v>
       </c>
       <c r="AL171">
-        <v>-19.010364</v>
+        <v>-19.176704</v>
       </c>
       <c r="AM171">
         <v>0.001022</v>
@@ -68766,7 +68760,7 @@
         <v>-0.213249</v>
       </c>
       <c r="AT171">
-        <v>-5.794361</v>
+        <v>-5.845063</v>
       </c>
     </row>
     <row r="172" spans="1:46">
@@ -68801,7 +68795,7 @@
         <v>853</v>
       </c>
       <c r="K172" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="L172">
         <v>168</v>
@@ -68858,7 +68852,7 @@
         <v>-6.12666667</v>
       </c>
       <c r="AD172" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE172">
         <v>-0.004444</v>
@@ -68882,7 +68876,7 @@
         <v>-0.313671</v>
       </c>
       <c r="AL172">
-        <v>-18.928538</v>
+        <v>-19.088667</v>
       </c>
       <c r="AM172">
         <v>-0.001367</v>
@@ -68906,7 +68900,7 @@
         <v>-0.314217</v>
       </c>
       <c r="AT172">
-        <v>-5.769417</v>
+        <v>-5.818225</v>
       </c>
     </row>
     <row r="173" spans="1:46">
@@ -68941,7 +68935,7 @@
         <v>854</v>
       </c>
       <c r="K173" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="L173">
         <v>138</v>
@@ -68998,7 +68992,7 @@
         <v>-6.07566667</v>
       </c>
       <c r="AD173" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE173">
         <v>0.005556</v>
@@ -69022,7 +69016,7 @@
         <v>-0.182674</v>
       </c>
       <c r="AL173">
-        <v>-18.7573</v>
+        <v>-18.889035</v>
       </c>
       <c r="AM173">
         <v>0.0017</v>
@@ -69046,7 +69040,7 @@
         <v>-0.182411</v>
       </c>
       <c r="AT173">
-        <v>-5.717223</v>
+        <v>-5.757378</v>
       </c>
     </row>
     <row r="174" spans="1:46">
@@ -69081,7 +69075,7 @@
         <v>855</v>
       </c>
       <c r="K174" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="L174">
         <v>193</v>
@@ -69138,7 +69132,7 @@
         <v>-6.11633333</v>
       </c>
       <c r="AD174" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE174">
         <v>-0.004444</v>
@@ -69162,7 +69156,7 @@
         <v>-0.3125</v>
       </c>
       <c r="AL174">
-        <v>-18.725601</v>
+        <v>-18.843899</v>
       </c>
       <c r="AM174">
         <v>-0.001356</v>
@@ -69186,7 +69180,7 @@
         <v>-0.312548</v>
       </c>
       <c r="AT174">
-        <v>-5.707559</v>
+        <v>-5.743617</v>
       </c>
     </row>
     <row r="175" spans="1:46">
@@ -69221,7 +69215,7 @@
         <v>856</v>
       </c>
       <c r="K175" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="L175">
         <v>240</v>
@@ -69278,7 +69272,7 @@
         <v>-6.1315</v>
       </c>
       <c r="AD175" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE175">
         <v>-0.000833</v>
@@ -69302,7 +69296,7 @@
         <v>-0.264319</v>
       </c>
       <c r="AL175">
-        <v>-18.719164</v>
+        <v>-18.833115</v>
       </c>
       <c r="AM175">
         <v>-0.000253</v>
@@ -69326,7 +69320,7 @@
         <v>-0.264293</v>
       </c>
       <c r="AT175">
-        <v>-5.705597</v>
+        <v>-5.74033</v>
       </c>
     </row>
     <row r="176" spans="1:46">
@@ -69361,7 +69355,7 @@
         <v>857</v>
       </c>
       <c r="K176" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="L176">
         <v>158</v>
@@ -69418,7 +69412,7 @@
         <v>-6.03533333</v>
       </c>
       <c r="AD176" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE176">
         <v>0.010556</v>
@@ -69442,7 +69436,7 @@
         <v>-0.114198</v>
       </c>
       <c r="AL176">
-        <v>-18.722907</v>
+        <v>-18.793101</v>
       </c>
       <c r="AM176">
         <v>0.003206</v>
@@ -69466,7 +69460,7 @@
         <v>-0.114679</v>
       </c>
       <c r="AT176">
-        <v>-5.706736</v>
+        <v>-5.728132</v>
       </c>
     </row>
     <row r="177" spans="1:46">
@@ -69501,7 +69495,7 @@
         <v>858</v>
       </c>
       <c r="K177" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="L177">
         <v>200</v>
@@ -69558,7 +69552,7 @@
         <v>-5.94366667</v>
       </c>
       <c r="AD177" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE177">
         <v>0.01</v>
@@ -69582,7 +69576,7 @@
         <v>-0.121176</v>
       </c>
       <c r="AL177">
-        <v>-18.752322</v>
+        <v>-18.803329</v>
       </c>
       <c r="AM177">
         <v>0.003056</v>
@@ -69606,7 +69600,7 @@
         <v>-0.120818</v>
       </c>
       <c r="AT177">
-        <v>-5.715701</v>
+        <v>-5.731249</v>
       </c>
     </row>
     <row r="178" spans="1:46">
@@ -69641,7 +69635,7 @@
         <v>859</v>
       </c>
       <c r="K178" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="L178">
         <v>255</v>
@@ -69698,7 +69692,7 @@
         <v>-5.913</v>
       </c>
       <c r="AD178" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE178">
         <v>0.003333</v>
@@ -69722,7 +69716,7 @@
         <v>-0.208743</v>
       </c>
       <c r="AL178">
-        <v>-18.763981</v>
+        <v>-18.809048</v>
       </c>
       <c r="AM178">
         <v>0.001022</v>
@@ -69746,7 +69740,7 @@
         <v>-0.208486</v>
       </c>
       <c r="AT178">
-        <v>-5.719253</v>
+        <v>-5.732991</v>
       </c>
     </row>
     <row r="179" spans="1:46">
@@ -69781,7 +69775,7 @@
         <v>860</v>
       </c>
       <c r="K179" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="L179">
         <v>186</v>
@@ -69838,7 +69832,7 @@
         <v>-5.94333333</v>
       </c>
       <c r="AD179" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE179">
         <v>-0.003333</v>
@@ -69862,7 +69856,7 @@
         <v>-0.296254</v>
       </c>
       <c r="AL179">
-        <v>-18.936508</v>
+        <v>-18.921204</v>
       </c>
       <c r="AM179">
         <v>-0.001011</v>
@@ -69886,7 +69880,7 @@
         <v>-0.29603</v>
       </c>
       <c r="AT179">
-        <v>-5.771836</v>
+        <v>-5.767172</v>
       </c>
     </row>
     <row r="180" spans="1:46">
@@ -69921,7 +69915,7 @@
         <v>861</v>
       </c>
       <c r="K180" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="L180">
         <v>270</v>
@@ -69978,7 +69972,7 @@
         <v>-5.94333333</v>
       </c>
       <c r="AD180" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE180">
         <v>0</v>
@@ -70002,7 +69996,7 @@
         <v>-0.251177</v>
       </c>
       <c r="AL180">
-        <v>-19.029837</v>
+        <v>-18.989995</v>
       </c>
       <c r="AM180">
         <v>0</v>
@@ -70026,7 +70020,7 @@
         <v>-0.251192</v>
       </c>
       <c r="AT180">
-        <v>-5.800281</v>
+        <v>-5.788138</v>
       </c>
     </row>
     <row r="181" spans="1:46">
@@ -70061,7 +70055,7 @@
         <v>862</v>
       </c>
       <c r="K181" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="L181">
         <v>144</v>
@@ -70118,7 +70112,7 @@
         <v>-6.07566667</v>
       </c>
       <c r="AD181" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE181">
         <v>-0.014444</v>
@@ -70142,7 +70136,7 @@
         <v>-0.442296</v>
       </c>
       <c r="AL181">
-        <v>-19.069828</v>
+        <v>-19.020302</v>
       </c>
       <c r="AM181">
         <v>-0.004411</v>
@@ -70166,7 +70160,7 @@
         <v>-0.442652</v>
       </c>
       <c r="AT181">
-        <v>-5.81247</v>
+        <v>-5.797375</v>
       </c>
     </row>
     <row r="182" spans="1:46">
@@ -70201,7 +70195,7 @@
         <v>863</v>
       </c>
       <c r="K182" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L182">
         <v>218</v>
@@ -70258,7 +70252,7 @@
         <v>-6.086</v>
       </c>
       <c r="AD182" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE182">
         <v>-0.001111</v>
@@ -70282,7 +70276,7 @@
         <v>-0.263335</v>
       </c>
       <c r="AL182">
-        <v>-19.417231</v>
+        <v>-19.295916</v>
       </c>
       <c r="AM182">
         <v>-0.000344</v>
@@ -70306,7 +70300,7 @@
         <v>-0.263584</v>
       </c>
       <c r="AT182">
-        <v>-5.91836</v>
+        <v>-5.881383</v>
       </c>
     </row>
     <row r="183" spans="1:46">
@@ -70341,7 +70335,7 @@
         <v>864</v>
       </c>
       <c r="K183" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L183">
         <v>310</v>
@@ -70398,7 +70392,7 @@
         <v>-6.03533333</v>
       </c>
       <c r="AD183" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE183">
         <v>0.005556</v>
@@ -70422,7 +70416,7 @@
         <v>-0.173512</v>
       </c>
       <c r="AL183">
-        <v>-19.565727</v>
+        <v>-19.418185</v>
       </c>
       <c r="AM183">
         <v>0.001689</v>
@@ -70446,7 +70440,7 @@
         <v>-0.173712</v>
       </c>
       <c r="AT183">
-        <v>-5.963625</v>
+        <v>-5.918652</v>
       </c>
     </row>
     <row r="184" spans="1:46">
@@ -70481,7 +70475,7 @@
         <v>865</v>
       </c>
       <c r="K184" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L184">
         <v>164</v>
@@ -70538,7 +70532,7 @@
         <v>-5.92333333</v>
       </c>
       <c r="AD184" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE184">
         <v>0.012222</v>
@@ -70562,7 +70556,7 @@
         <v>-0.083727</v>
       </c>
       <c r="AL184">
-        <v>-19.615619</v>
+        <v>-19.459701</v>
       </c>
       <c r="AM184">
         <v>0.003733</v>
@@ -70586,7 +70580,7 @@
         <v>-0.083359</v>
       </c>
       <c r="AT184">
-        <v>-5.978825</v>
+        <v>-5.931301</v>
       </c>
     </row>
     <row r="185" spans="1:46">
@@ -70621,7 +70615,7 @@
         <v>866</v>
       </c>
       <c r="K185" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="L185">
         <v>225</v>
@@ -70678,7 +70672,7 @@
         <v>-5.88266667</v>
       </c>
       <c r="AD185" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE185">
         <v>0.004444</v>
@@ -70702,7 +70696,7 @@
         <v>-0.187973</v>
       </c>
       <c r="AL185">
-        <v>-20.094647</v>
+        <v>-19.867371</v>
       </c>
       <c r="AM185">
         <v>0.001356</v>
@@ -70726,7 +70720,7 @@
         <v>-0.187902</v>
       </c>
       <c r="AT185">
-        <v>-6.124835</v>
+        <v>-6.05556</v>
       </c>
     </row>
     <row r="186" spans="1:46">
@@ -70761,7 +70755,7 @@
         <v>867</v>
       </c>
       <c r="K186" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="L186">
         <v>157</v>
@@ -70818,7 +70812,7 @@
         <v>-5.96366667</v>
       </c>
       <c r="AD186" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE186">
         <v>-0.008888999999999999</v>
@@ -70842,7 +70836,7 @@
         <v>-0.366939</v>
       </c>
       <c r="AL186">
-        <v>-20.29168</v>
+        <v>-20.039243</v>
       </c>
       <c r="AM186">
         <v>-0.0027</v>
@@ -70866,7 +70860,7 @@
         <v>-0.366532</v>
       </c>
       <c r="AT186">
-        <v>-6.184884</v>
+        <v>-6.10794</v>
       </c>
     </row>
     <row r="187" spans="1:46">
@@ -70901,7 +70895,7 @@
         <v>868</v>
       </c>
       <c r="K187" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L187">
         <v>198</v>
@@ -70958,7 +70952,7 @@
         <v>-6.00466667</v>
       </c>
       <c r="AD187" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE187">
         <v>-0.004444</v>
@@ -70982,7 +70976,7 @@
         <v>-0.305857</v>
       </c>
       <c r="AL187">
-        <v>-20.357614</v>
+        <v>-20.097274</v>
       </c>
       <c r="AM187">
         <v>-0.001367</v>
@@ -71006,7 +71000,7 @@
         <v>-0.306421</v>
       </c>
       <c r="AT187">
-        <v>-6.204987</v>
+        <v>-6.125633</v>
       </c>
     </row>
     <row r="188" spans="1:46">
@@ -71041,7 +71035,7 @@
         <v>869</v>
       </c>
       <c r="K188" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="L188">
         <v>146</v>
@@ -71098,7 +71092,7 @@
         <v>-6.01466667</v>
       </c>
       <c r="AD188" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE188">
         <v>-0.001111</v>
@@ -71122,7 +71116,7 @@
         <v>-0.259862</v>
       </c>
       <c r="AL188">
-        <v>-20.891537</v>
+        <v>-20.577464</v>
       </c>
       <c r="AM188">
         <v>-0.000333</v>
@@ -71146,7 +71140,7 @@
         <v>-0.25961</v>
       </c>
       <c r="AT188">
-        <v>-6.367724</v>
+        <v>-6.271992</v>
       </c>
     </row>
     <row r="189" spans="1:46">
@@ -71181,7 +71175,7 @@
         <v>870</v>
       </c>
       <c r="K189" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="L189">
         <v>193</v>
@@ -71238,7 +71232,7 @@
         <v>-6.035</v>
       </c>
       <c r="AD189" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE189">
         <v>-0.002222</v>
@@ -71262,7 +71256,7 @@
         <v>-0.274193</v>
       </c>
       <c r="AL189">
-        <v>-21.088478</v>
+        <v>-20.760118</v>
       </c>
       <c r="AM189">
         <v>-0.000678</v>
@@ -71286,7 +71280,7 @@
         <v>-0.274225</v>
       </c>
       <c r="AT189">
-        <v>-6.427745</v>
+        <v>-6.327659</v>
       </c>
     </row>
     <row r="190" spans="1:46">
@@ -71321,7 +71315,7 @@
         <v>871</v>
       </c>
       <c r="K190" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="L190">
         <v>213</v>
@@ -71378,7 +71372,7 @@
         <v>-6.035</v>
       </c>
       <c r="AD190" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE190">
         <v>0</v>
@@ -71402,7 +71396,7 @@
         <v>-0.2432</v>
       </c>
       <c r="AL190">
-        <v>-21.15017</v>
+        <v>-20.818148</v>
       </c>
       <c r="AM190">
         <v>0</v>
@@ -71426,7 +71420,7 @@
         <v>-0.243191</v>
       </c>
       <c r="AT190">
-        <v>-6.446555</v>
+        <v>-6.345353</v>
       </c>
     </row>
     <row r="191" spans="1:46">
@@ -71461,7 +71455,7 @@
         <v>872</v>
       </c>
       <c r="K191" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L191">
         <v>171</v>
@@ -71518,7 +71512,7 @@
         <v>-6.106</v>
       </c>
       <c r="AD191" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE191">
         <v>-0.007778</v>
@@ -71542,7 +71536,7 @@
         <v>-0.34854</v>
       </c>
       <c r="AL191">
-        <v>-21.584372</v>
+        <v>-21.245199</v>
       </c>
       <c r="AM191">
         <v>-0.002367</v>
@@ -71566,7 +71560,7 @@
         <v>-0.34837</v>
       </c>
       <c r="AT191">
-        <v>-6.578896</v>
+        <v>-6.475513</v>
       </c>
     </row>
     <row r="192" spans="1:46">
@@ -71601,7 +71595,7 @@
         <v>873</v>
       </c>
       <c r="K192" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L192">
         <v>207</v>
@@ -71658,7 +71652,7 @@
         <v>-6.157</v>
       </c>
       <c r="AD192" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE192">
         <v>-0.005556</v>
@@ -71682,7 +71676,7 @@
         <v>-0.317165</v>
       </c>
       <c r="AL192">
-        <v>-21.702423</v>
+        <v>-21.374118</v>
       </c>
       <c r="AM192">
         <v>-0.0017</v>
@@ -71706,7 +71700,7 @@
         <v>-0.317465</v>
       </c>
       <c r="AT192">
-        <v>-6.614881</v>
+        <v>-6.51481</v>
       </c>
     </row>
     <row r="193" spans="1:46">
@@ -71741,7 +71735,7 @@
         <v>874</v>
       </c>
       <c r="K193" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="L193">
         <v>173</v>
@@ -71798,7 +71792,7 @@
         <v>-6.167</v>
       </c>
       <c r="AD193" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE193">
         <v>-0.001111</v>
@@ -71822,7 +71816,7 @@
         <v>-0.255369</v>
       </c>
       <c r="AL193">
-        <v>-21.731971</v>
+        <v>-21.409115</v>
       </c>
       <c r="AM193">
         <v>-0.000333</v>
@@ -71846,7 +71840,7 @@
         <v>-0.255118</v>
       </c>
       <c r="AT193">
-        <v>-6.623887</v>
+        <v>-6.525478</v>
       </c>
     </row>
     <row r="194" spans="1:46">
@@ -71881,7 +71875,7 @@
         <v>875</v>
       </c>
       <c r="K194" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="L194">
         <v>203</v>
@@ -71938,7 +71932,7 @@
         <v>-5.964</v>
       </c>
       <c r="AD194" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE194">
         <v>0.022222</v>
@@ -71962,7 +71956,7 @@
         <v>0.065863</v>
       </c>
       <c r="AL194">
-        <v>-21.691801</v>
+        <v>-21.503093</v>
       </c>
       <c r="AM194">
         <v>0.006767</v>
@@ -71986,7 +71980,7 @@
         <v>0.065564</v>
       </c>
       <c r="AT194">
-        <v>-6.61165</v>
+        <v>-6.554128</v>
       </c>
     </row>
     <row r="195" spans="1:46">
@@ -72021,7 +72015,7 @@
         <v>876</v>
       </c>
       <c r="K195" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="L195">
         <v>137</v>
@@ -72078,7 +72072,7 @@
         <v>-6.04016667</v>
       </c>
       <c r="AD195" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE195">
         <v>-0.004167</v>
@@ -72102,7 +72096,7 @@
         <v>-0.297746</v>
       </c>
       <c r="AL195">
-        <v>-20.915718</v>
+        <v>-20.978772</v>
       </c>
       <c r="AM195">
         <v>-0.001269</v>
@@ -72126,7 +72120,7 @@
         <v>-0.297724</v>
       </c>
       <c r="AT195">
-        <v>-6.375109</v>
+        <v>-6.394324</v>
       </c>
     </row>
     <row r="196" spans="1:46">
@@ -72161,7 +72155,7 @@
         <v>877</v>
       </c>
       <c r="K196" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="L196">
         <v>205</v>
@@ -72218,7 +72212,7 @@
         <v>-5.98433333</v>
       </c>
       <c r="AD196" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE196">
         <v>0.006111</v>
@@ -72242,7 +72236,7 @@
         <v>-0.155053</v>
       </c>
       <c r="AL196">
-        <v>-20.462325</v>
+        <v>-20.64167</v>
       </c>
       <c r="AM196">
         <v>0.001861</v>
@@ -72266,7 +72260,7 @@
         <v>-0.155139</v>
       </c>
       <c r="AT196">
-        <v>-6.236905</v>
+        <v>-6.29157</v>
       </c>
     </row>
     <row r="197" spans="1:46">
@@ -72301,7 +72295,7 @@
         <v>878</v>
       </c>
       <c r="K197" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="L197">
         <v>176</v>
@@ -72358,7 +72352,7 @@
         <v>-6.17733333</v>
       </c>
       <c r="AD197" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE197">
         <v>-0.021111</v>
@@ -72382,7 +72376,7 @@
         <v>-0.531111</v>
       </c>
       <c r="AL197">
-        <v>-18.055567</v>
+        <v>-18.765466</v>
       </c>
       <c r="AM197">
         <v>-0.006433</v>
@@ -72406,7 +72400,7 @@
         <v>-0.531043</v>
       </c>
       <c r="AT197">
-        <v>-5.503342</v>
+        <v>-5.71972</v>
       </c>
     </row>
     <row r="198" spans="1:46">
@@ -72441,7 +72435,7 @@
         <v>879</v>
       </c>
       <c r="K198" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L198">
         <v>206</v>
@@ -72498,7 +72492,7 @@
         <v>-6.08566667</v>
       </c>
       <c r="AD198" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE198">
         <v>0.01</v>
@@ -72522,7 +72516,7 @@
         <v>-0.098276</v>
       </c>
       <c r="AL198">
-        <v>-17.039282</v>
+        <v>-17.952951</v>
       </c>
       <c r="AM198">
         <v>0.003056</v>
@@ -72546,7 +72540,7 @@
         <v>-0.09791900000000001</v>
       </c>
       <c r="AT198">
-        <v>-5.193608</v>
+        <v>-5.472091</v>
       </c>
     </row>
     <row r="199" spans="1:46">
@@ -72581,7 +72575,7 @@
         <v>880</v>
       </c>
       <c r="K199" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="L199">
         <v>160</v>
@@ -72638,7 +72632,7 @@
         <v>-5.90633333</v>
       </c>
       <c r="AD199" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE199">
         <v>0.006543</v>
@@ -72662,7 +72656,7 @@
         <v>-0.146093</v>
       </c>
       <c r="AL199">
-        <v>-16.881555</v>
+        <v>-17.826211</v>
       </c>
       <c r="AM199">
         <v>0.001993</v>
@@ -72686,7 +72680,7 @@
         <v>-0.146171</v>
       </c>
       <c r="AT199">
-        <v>-5.145544</v>
+        <v>-5.43347</v>
       </c>
     </row>
     <row r="200" spans="1:46">
@@ -72721,7 +72715,7 @@
         <v>881</v>
       </c>
       <c r="K200" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="L200">
         <v>65</v>
@@ -72778,7 +72772,7 @@
         <v>-5.10033333</v>
       </c>
       <c r="AD200" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE200">
         <v>0.088148</v>
@@ -72802,7 +72796,7 @@
         <v>0.989351</v>
       </c>
       <c r="AL200">
-        <v>-13.303298</v>
+        <v>-14.91969</v>
       </c>
       <c r="AM200">
         <v>0.026867</v>
@@ -72826,7 +72820,7 @@
         <v>0.989362</v>
       </c>
       <c r="AT200">
-        <v>-4.054861</v>
+        <v>-4.547542</v>
       </c>
     </row>
     <row r="201" spans="1:46">
@@ -72861,7 +72855,7 @@
         <v>882</v>
       </c>
       <c r="K201" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="L201">
         <v>100</v>
@@ -72918,7 +72912,7 @@
         <v>-5.30366667</v>
       </c>
       <c r="AD201" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE201">
         <v>-0.022222</v>
@@ -72942,7 +72936,7 @@
         <v>-0.55131</v>
       </c>
       <c r="AL201">
-        <v>-11.259639</v>
+        <v>-13.241098</v>
       </c>
       <c r="AM201">
         <v>-0.006778</v>
@@ -72966,7 +72960,7 @@
         <v>-0.551559</v>
       </c>
       <c r="AT201">
-        <v>-3.431947</v>
+        <v>-4.035904</v>
       </c>
     </row>
     <row r="202" spans="1:46">
@@ -73001,7 +72995,7 @@
         <v>883</v>
       </c>
       <c r="K202" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="L202">
         <v>135</v>
@@ -73058,7 +73052,7 @@
         <v>-5.47633333</v>
       </c>
       <c r="AD202" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE202">
         <v>-0.018889</v>
@@ -73082,7 +73076,7 @@
         <v>-0.503072</v>
       </c>
       <c r="AL202">
-        <v>-10.735588</v>
+        <v>-12.809108</v>
       </c>
       <c r="AM202">
         <v>-0.005756</v>
@@ -73106,7 +73100,7 @@
         <v>-0.503037</v>
       </c>
       <c r="AT202">
-        <v>-3.272258</v>
+        <v>-3.90427</v>
       </c>
     </row>
     <row r="203" spans="1:46">
@@ -73141,7 +73135,7 @@
         <v>884</v>
       </c>
       <c r="K203" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="L203">
         <v>117</v>
@@ -73198,7 +73192,7 @@
         <v>-0.23027778</v>
       </c>
       <c r="AD203" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AE203">
         <v>0.09561699999999999</v>
@@ -73222,7 +73216,7 @@
         <v>1.096969</v>
       </c>
       <c r="AL203">
-        <v>-9.181698000000001</v>
+        <v>-11.525067</v>
       </c>
       <c r="AM203">
         <v>0.029145</v>
@@ -73246,147 +73240,7 @@
         <v>1.097001</v>
       </c>
       <c r="AT203">
-        <v>-2.798639</v>
-      </c>
-    </row>
-    <row r="204" spans="1:46">
-      <c r="A204" t="s">
-        <v>37</v>
-      </c>
-      <c r="B204" t="s">
-        <v>91</v>
-      </c>
-      <c r="C204" s="2">
-        <v>45507.41617234953</v>
-      </c>
-      <c r="D204" s="2">
-        <v>45507.41614583333</v>
-      </c>
-      <c r="E204">
-        <v>5621</v>
-      </c>
-      <c r="F204">
-        <v>1713.28</v>
-      </c>
-      <c r="G204">
-        <v>-25.4</v>
-      </c>
-      <c r="H204">
-        <v>2490</v>
-      </c>
-      <c r="I204" t="s">
-        <v>682</v>
-      </c>
-      <c r="J204" t="s">
-        <v>885</v>
-      </c>
-      <c r="K204" t="s">
-        <v>1088</v>
-      </c>
-      <c r="L204">
-        <v>83</v>
-      </c>
-      <c r="M204">
-        <v>0</v>
-      </c>
-      <c r="N204">
-        <v>0</v>
-      </c>
-      <c r="O204">
-        <v>38.8186666667</v>
-      </c>
-      <c r="P204">
-        <v>-103.9661666667</v>
-      </c>
-      <c r="Q204">
-        <v>27.05</v>
-      </c>
-      <c r="R204">
-        <v>43.53</v>
-      </c>
-      <c r="S204">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="T204">
-        <v>18</v>
-      </c>
-      <c r="U204">
-        <v>291.15</v>
-      </c>
-      <c r="V204">
-        <v>83680</v>
-      </c>
-      <c r="W204">
-        <v>0.83</v>
-      </c>
-      <c r="X204">
-        <v>0.00194277</v>
-      </c>
-      <c r="Y204">
-        <v>1.00126106</v>
-      </c>
-      <c r="Z204">
-        <v>7.9E-07</v>
-      </c>
-      <c r="AA204">
-        <v>-7.9E-07</v>
-      </c>
-      <c r="AB204">
-        <v>-0.42380952</v>
-      </c>
-      <c r="AC204">
-        <v>-0.12919048</v>
-      </c>
-      <c r="AD204" t="s">
-        <v>1089</v>
-      </c>
-      <c r="AE204">
-        <v>0.00158</v>
-      </c>
-      <c r="AF204">
-        <v>-36.25879</v>
-      </c>
-      <c r="AG204">
-        <v>0.01729</v>
-      </c>
-      <c r="AH204">
-        <v>22.753432</v>
-      </c>
-      <c r="AI204">
-        <v>0.071163</v>
-      </c>
-      <c r="AJ204">
-        <v>1.574926</v>
-      </c>
-      <c r="AK204">
-        <v>-0.220761</v>
-      </c>
-      <c r="AL204">
-        <v>-9.359890999999999</v>
-      </c>
-      <c r="AM204">
-        <v>0.000481</v>
-      </c>
-      <c r="AN204">
-        <v>-11.051679</v>
-      </c>
-      <c r="AO204">
-        <v>0.00527</v>
-      </c>
-      <c r="AP204">
-        <v>6.935245</v>
-      </c>
-      <c r="AQ204">
-        <v>0.02169</v>
-      </c>
-      <c r="AR204">
-        <v>1.574925</v>
-      </c>
-      <c r="AS204">
-        <v>-0.220793</v>
-      </c>
-      <c r="AT204">
-        <v>-2.852906</v>
+        <v>-3.512901</v>
       </c>
     </row>
   </sheetData>

--- a/www/flightdata/xlsx/eoss-361.xlsx
+++ b/www/flightdata/xlsx/eoss-361.xlsx
@@ -3786,7 +3786,7 @@
         <v>30216.65</v>
       </c>
       <c r="I2">
-        <v>750</v>
+        <v>494</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
